--- a/04_DESIGN_TABLES/DesignTable_2406_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2406_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL41"/>
+  <dimension ref="A1:AL52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,35 +742,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2406-04-06</t>
+          <t>2406-03-04</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="C3" t="n">
-        <v>0.36373</v>
+        <v>0.28868</v>
       </c>
       <c r="D3" t="n">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="F3" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="K3" t="n">
         <v>60</v>
@@ -779,64 +779,64 @@
         <v>37</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4495</v>
+        <v>0.4538</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="R3" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2215</v>
+        <v>0.19</v>
       </c>
       <c r="T3" t="n">
-        <v>0.19169</v>
+        <v>0.16495</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2982</v>
+        <v>0.241</v>
       </c>
       <c r="V3" t="n">
-        <v>0.38338</v>
+        <v>0.3299</v>
       </c>
       <c r="W3" t="n">
-        <v>0.328</v>
+        <v>0.266</v>
       </c>
       <c r="X3" t="n">
-        <v>0.05</v>
+        <v>0.04167</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.19169</v>
+        <v>0.16495</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.21875</v>
+        <v>0.1875</v>
       </c>
       <c r="AA3" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.17</v>
+        <v>0.125</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.672</v>
+        <v>0.714</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2406-04-06</t>
+          <t>2406-03-04</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 9/16-18 x 7/16-20 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 7/16-20 x 3/8-24 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>9/16-18</t>
+          <t>7/16-20</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>7/16-20 (female 37deg JIC)</t>
+          <t>3/8-24 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -861,52 +861,52 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L23@DRIVE: Brennan TFA catalog p7 table TFA-p007-t03 "2406 FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)" row 2406-03-04 col "L0 LGTH" = "0.980" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 183.5, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p7 2406 drawing: L0 spans the whole part (female face to male JIC tip), C HEX = body hex, B2 DRILL = male-end bore (impact/F2a.json certain; drawing re-read 2026-10-18, verify/png/TFA_p07_RT.png); same-table check on today's base: 16/47 rows with an Air-Way/OMi value agree with this catalog column to rounding (31 differ, e.g. 2406-04-05 1.0 vs 1.15); HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t03 "2406 FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)" row 2406-03-04 col "C HEX" = "0.500" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 183.5, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p7 2406 drawing: L0 spans the whole part (female face to male JIC tip), C HEX = body hex, B2 DRILL = male-end bore (impact/F2a.json certain; drawing re-read 2026-10-18, verify/png/TFA_p07_RT.png); same-table check on today's base: 46/47 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 2406-04-05 0.56 vs 0.625); D3@BORE: Brennan TFA catalog p7 table TFA-p007-t03 "2406 FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)" row 2406-03-04 col "B2 DRILL" = "0.125" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 183.5, page verified) [Brennan = yes 2026-10-18] - male-end bore; mapping: TFA p7 2406 drawing: L0 spans the whole part (female face to male JIC tip), C HEX = body hex, B2 DRILL = male-end bore (impact/F2a.json certain; drawing re-read 2026-10-18, verify/png/TFA_p07_RT.png); same-table check on today's base: 45/47 rows with an Air-Way/OMi value agree with this catalog column to rounding (2 differ, e.g. 2406-05-06 0.3 vs 0.234); THDMAJ_A@DRIVE: end library gen_straight2 JIC[3] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major of the female end (first dash); THDMAJ_B@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major of the male end (second dash); JICB_RELIEFL@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JICB_THDZ@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JICB_CONEDIA@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JICB_LANDL@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JICB_SEATL@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); RELIEFANG@DRIVE: gen_straight2 end_JICM constant 60 deg relief ramp (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; SEATB@DRIVE: gen_straight2 end_JICM constant 37 deg flare seat (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; $PRP@EndA_Thread: end library gen_straight2 JIC[3] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text (format of the built 2406 rows); $PRP@EndB_Thread: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.418 from the End A tip, inside the End A thread/groove zone (0.556); radial wall there min 0.136 at 0.556 from the tip (OK)</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L23 / hex / D3 from the Brennan TFA catalog p7 alone (built 2406 rows are Air-Way; Brennan L0 equals their L23 on 16/47 only - different bodies, see wave2 REPORT); female -03 port = JICF_MEAS[3] (Brennan 2406-03-04 STEP, already in the end library)</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2406-04-06</t>
+          <t>2406-03-04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2406-05-04</t>
+          <t>2406-04-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="C4" t="n">
-        <v>0.36373</v>
+        <v>0.32505</v>
       </c>
       <c r="D4" t="n">
-        <v>0.63</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.21875</v>
+        <v>0.15625</v>
       </c>
       <c r="F4" t="n">
-        <v>0.075</v>
+        <v>0.063</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2608</v>
+        <v>0.19</v>
       </c>
       <c r="H4" t="n">
-        <v>0.182</v>
+        <v>0.125</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0795</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1135</v>
+        <v>0.1108</v>
       </c>
       <c r="K4" t="n">
         <v>60</v>
@@ -915,64 +915,64 @@
         <v>37</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4375</v>
+        <v>0.3125</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05</v>
+        <v>0.04167</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4538</v>
+        <v>0.367</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02706</v>
+        <v>0.02255</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0125</v>
+        <v>0.01042</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05</v>
+        <v>0.04167</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2525</v>
+        <v>0.2215</v>
       </c>
       <c r="T4" t="n">
-        <v>0.22294</v>
+        <v>0.19169</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3144</v>
+        <v>0.2982</v>
       </c>
       <c r="V4" t="n">
-        <v>0.44588</v>
+        <v>0.38338</v>
       </c>
       <c r="W4" t="n">
-        <v>0.344</v>
+        <v>0.328</v>
       </c>
       <c r="X4" t="n">
         <v>0.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.22294</v>
+        <v>0.19169</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.25</v>
+        <v>0.21875</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.17</v>
+        <v>0.062</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.846</v>
+        <v>0.712</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2406-05-04</t>
+          <t>2406-04-02</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 7/16-20 x 1/2-20 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 5/16-24 x 7/16-20 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>7/16-20</t>
+          <t>5/16-24</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1/2-20 (female 37deg JIC)</t>
+          <t>7/16-20 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -997,52 +997,52 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L23@DRIVE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-04-02 column 'L0 LGTH' = 1.04 (catalog_verified.json); OMi Items row 571: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-04-02 column 'C HEX' = 0.563 (catalog_verified.json); OMi Items row 571: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D3@BORE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-04-02 column 'B2 DRILL' = 0.062 (catalog_verified.json); OMi Items row 571: no dimension; no Air-Way row; equals the 2026-10-02 proposal; THDMAJ_A@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, female end (first dash); catalog B1 7/16-20; equals the 2026-10-02 proposal; THDMAJ_B@DRIVE: gen_straight2 JIC[2] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male end (second dash); catalog B2 5/16-24; equals the 2026-10-02 proposal; JICB_RELIEFL@DRIVE: gen_straight2 JIC[2] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) RL; equals the 2026-10-02 proposal; JICB_THDZ@DRIVE: gen_straight2 JIC[2] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) TZ; equals the 2026-10-02 proposal; JICB_CONEDIA@DRIVE: gen_straight2 JIC[2] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) CD; equals the 2026-10-02 proposal; JICB_LANDL@DRIVE: gen_straight2 JIC[2] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) LL; equals the 2026-10-02 proposal; JICB_SEATL@DRIVE: gen_straight2 JIC[2] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) SL; equals the 2026-10-02 proposal; RELIEFANG@DRIVE: gen_straight2 end_JICM constant (60 deg relief ramp, every 2406 row); equals the 2026-10-02 proposal; SEATB@DRIVE: gen_straight2 end_JICM constant (37 deg flare seat, every 2406 row); equals the 2026-10-02 proposal; $PRP@EndA_Thread: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text (format of the built 2406 rows); equals the 2026-10-02 proposal; $PRP@EndB_Thread: gen_straight2 JIC[2] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text; equals the 2026-10-02 proposal | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone; built rows of this table are Air-Way</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2406-05-04</t>
+          <t>2406-04-02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2406-05-06</t>
+          <t>2406-04-04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.36373</v>
+        <v>0.32447</v>
       </c>
       <c r="D5" t="n">
-        <v>0.63</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="F5" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="K5" t="n">
         <v>60</v>
@@ -1051,64 +1051,64 @@
         <v>37</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="N5" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4495</v>
+        <v>0.4538</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2525</v>
+        <v>0.2215</v>
       </c>
       <c r="T5" t="n">
-        <v>0.22294</v>
+        <v>0.19169</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3144</v>
+        <v>0.2982</v>
       </c>
       <c r="V5" t="n">
-        <v>0.44588</v>
+        <v>0.38338</v>
       </c>
       <c r="W5" t="n">
-        <v>0.344</v>
+        <v>0.328</v>
       </c>
       <c r="X5" t="n">
         <v>0.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.22294</v>
+        <v>0.19169</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.25</v>
+        <v>0.21875</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3</v>
+        <v>0.172</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.846</v>
+        <v>0.822</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2406-05-06</t>
+          <t>2406-04-04</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 9/16-18 x 1/2-20 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 7/16-20 x 7/16-20 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>9/16-18</t>
+          <t>7/16-20</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1/2-20 (female 37deg JIC)</t>
+          <t>7/16-20 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1133,52 +1133,52 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L23@DRIVE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-04-04 column 'L0 LGTH' = 1.15 (catalog_verified.json); OMi Items row 572: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-04-04 column 'C HEX' = 0.562 (catalog_verified.json); OMi Items row 572: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D3@BORE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-04-04 column 'B2 DRILL' = 0.172 (catalog_verified.json); OMi Items row 572: no dimension; no Air-Way row; equals the 2026-10-02 proposal; THDMAJ_A@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, female end (first dash); catalog B1 7/16-20; equals the 2026-10-02 proposal; THDMAJ_B@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male end (second dash); catalog B2 7/16-20; equals the 2026-10-02 proposal; JICB_RELIEFL@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) RL; equals the 2026-10-02 proposal; JICB_THDZ@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) TZ; equals the 2026-10-02 proposal; JICB_CONEDIA@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) CD; equals the 2026-10-02 proposal; JICB_LANDL@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) LL; equals the 2026-10-02 proposal; JICB_SEATL@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) SL; equals the 2026-10-02 proposal; RELIEFANG@DRIVE: gen_straight2 end_JICM constant (60 deg relief ramp, every 2406 row); equals the 2026-10-02 proposal; SEATB@DRIVE: gen_straight2 end_JICM constant (37 deg flare seat, every 2406 row); equals the 2026-10-02 proposal; $PRP@EndA_Thread: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text (format of the built 2406 rows); equals the 2026-10-02 proposal; $PRP@EndB_Thread: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text; equals the 2026-10-02 proposal | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone; built rows of this table are Air-Way</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2406-05-06</t>
+          <t>2406-04-04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2406-06-04</t>
+          <t>2406-04-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.39837</v>
+        <v>0.36373</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="E6" t="n">
-        <v>0.21875</v>
+        <v>0.28125</v>
       </c>
       <c r="F6" t="n">
-        <v>0.075</v>
+        <v>0.083</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2608</v>
+        <v>0.2515</v>
       </c>
       <c r="H6" t="n">
-        <v>0.182</v>
+        <v>0.2405</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0795</v>
+        <v>0.0898</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1135</v>
+        <v>0.1082</v>
       </c>
       <c r="K6" t="n">
         <v>60</v>
@@ -1187,64 +1187,64 @@
         <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4375</v>
+        <v>0.5625</v>
       </c>
       <c r="N6" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.2215</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.19169</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="X6" t="n">
         <v>0.05</v>
       </c>
-      <c r="O6" t="n">
-        <v>0.4538</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.02706</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.2835</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.25118</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.3117</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.50236</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.05556</v>
-      </c>
       <c r="Y6" t="n">
-        <v>0.25118</v>
+        <v>0.19169</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AB6" t="n">
         <v>0.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.846</v>
+        <v>0.672</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2406-06-04</t>
+          <t>2406-04-06</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 7/16-20 x 9/16-18 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 9/16-18 x 7/16-20 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>7/16-20</t>
+          <t>9/16-18</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9/16-18 (female 37deg JIC)</t>
+          <t>7/16-20 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1274,47 +1274,47 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.418 from the End A tip, inside the End A thread/groove zone (0.556); radial wall there min 0.136 at 0.556 from the tip (OK)</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2406-06-04</t>
+          <t>2406-04-06</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2406-06-05</t>
+          <t>2406-04-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="C7" t="n">
-        <v>0.39837</v>
+        <v>0.46881</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="F7" t="n">
-        <v>0.075</v>
+        <v>0.094</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2606</v>
+        <v>0.2837</v>
       </c>
       <c r="H7" t="n">
-        <v>0.213</v>
+        <v>0.3295</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0795</v>
+        <v>0.0984</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1135</v>
+        <v>0.1546</v>
       </c>
       <c r="K7" t="n">
         <v>60</v>
@@ -1323,64 +1323,64 @@
         <v>37</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="N7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.5367</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.2215</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.19169</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="X7" t="n">
         <v>0.05</v>
       </c>
-      <c r="O7" t="n">
-        <v>0.4536</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.02706</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.2835</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.25118</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.3117</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.50236</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.05556</v>
-      </c>
       <c r="Y7" t="n">
-        <v>0.25118</v>
+        <v>0.19169</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.23</v>
+        <v>0.172</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.846</v>
+        <v>0.922</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2406-06-05</t>
+          <t>2406-04-08</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1/2-20 x 9/16-18 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 3/4-16 x 7/16-20 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1390,12 +1390,12 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>1/2-20</t>
+          <t>3/4-16</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>9/16-18 (female 37deg JIC)</t>
+          <t>7/16-20 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -1405,52 +1405,52 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L23@DRIVE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-04-08 column 'L0 LGTH' = 1.25 (catalog_verified.json); OMi Items row 574: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-04-08 column 'C HEX' = 0.812 (catalog_verified.json); OMi Items row 574: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D3@BORE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-04-08 column 'B2 DRILL' = 0.172 (catalog_verified.json); OMi Items row 574: no dimension; no Air-Way row; equals the 2026-10-02 proposal; THDMAJ_A@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, female end (first dash); catalog B1 7/16-20; equals the 2026-10-02 proposal; THDMAJ_B@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male end (second dash); catalog B2 3/4-16; equals the 2026-10-02 proposal; JICB_RELIEFL@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) RL; equals the 2026-10-02 proposal; JICB_THDZ@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) TZ; equals the 2026-10-02 proposal; JICB_CONEDIA@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) CD; equals the 2026-10-02 proposal; JICB_LANDL@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) LL; equals the 2026-10-02 proposal; JICB_SEATL@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) SL; equals the 2026-10-02 proposal; RELIEFANG@DRIVE: gen_straight2 end_JICM constant (60 deg relief ramp, every 2406 row); equals the 2026-10-02 proposal; SEATB@DRIVE: gen_straight2 end_JICM constant (37 deg flare seat, every 2406 row); equals the 2026-10-02 proposal; $PRP@EndA_Thread: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text (format of the built 2406 rows); equals the 2026-10-02 proposal; $PRP@EndB_Thread: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text; equals the 2026-10-02 proposal | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone; built rows of this table are Air-Way</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2406-06-05</t>
+          <t>2406-04-08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2406-06-06</t>
+          <t>2406-05-04</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="C8" t="n">
-        <v>0.39837</v>
+        <v>0.36373</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="E8" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="F8" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="K8" t="n">
         <v>60</v>
@@ -1459,64 +1459,64 @@
         <v>37</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="N8" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4495</v>
+        <v>0.4538</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="R8" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2835</v>
+        <v>0.2525</v>
       </c>
       <c r="T8" t="n">
-        <v>0.25118</v>
+        <v>0.22294</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3117</v>
+        <v>0.3144</v>
       </c>
       <c r="V8" t="n">
-        <v>0.50236</v>
+        <v>0.44588</v>
       </c>
       <c r="W8" t="n">
         <v>0.344</v>
       </c>
       <c r="X8" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.25118</v>
+        <v>0.22294</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.28125</v>
+        <v>0.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.786</v>
+        <v>0.846</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2406-06-06</t>
+          <t>2406-05-04</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 9/16-18 x 9/16-18 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 7/16-20 x 1/2-20 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>9/16-18</t>
+          <t>7/16-20</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>9/16-18 (female 37deg JIC)</t>
+          <t>1/2-20 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -1551,42 +1551,42 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2406-06-06</t>
+          <t>2406-05-04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2406-06-08</t>
+          <t>2406-05-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="C9" t="n">
-        <v>0.46765</v>
+        <v>0.36373</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="E9" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="F9" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2837</v>
+        <v>0.2515</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3295</v>
+        <v>0.2405</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0984</v>
+        <v>0.0898</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="K9" t="n">
         <v>60</v>
@@ -1595,64 +1595,64 @@
         <v>37</v>
       </c>
       <c r="M9" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5367</v>
+        <v>0.4495</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03383</v>
+        <v>0.03007</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01562</v>
+        <v>0.01389</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2835</v>
+        <v>0.2525</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25118</v>
+        <v>0.22294</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3117</v>
+        <v>0.3144</v>
       </c>
       <c r="V9" t="n">
-        <v>0.50236</v>
+        <v>0.44588</v>
       </c>
       <c r="W9" t="n">
         <v>0.344</v>
       </c>
       <c r="X9" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.25118</v>
+        <v>0.22294</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.28125</v>
+        <v>0.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AB9" t="n">
         <v>0.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.846</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2406-06-08</t>
+          <t>2406-05-06</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 3/4-16 x 9/16-18 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 9/16-18 x 1/2-20 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>3/4-16</t>
+          <t>9/16-18</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>9/16-18 (female 37deg JIC)</t>
+          <t>1/2-20 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -1687,24 +1687,24 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2406-06-08</t>
+          <t>2406-05-06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2406-08-04</t>
+          <t>2406-06-04</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="C10" t="n">
-        <v>0.50807</v>
+        <v>0.39837</v>
       </c>
       <c r="D10" t="n">
-        <v>0.88</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E10" t="n">
         <v>0.21875</v>
@@ -1749,46 +1749,46 @@
         <v>0.05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3775</v>
+        <v>0.2835</v>
       </c>
       <c r="T10" t="n">
-        <v>0.34117</v>
+        <v>0.25118</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3387</v>
+        <v>0.3117</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6823399999999999</v>
+        <v>0.50236</v>
       </c>
       <c r="W10" t="n">
-        <v>0.375</v>
+        <v>0.344</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.34117</v>
+        <v>0.25118</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AB10" t="n">
         <v>0.17</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.955</v>
+        <v>0.846</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2406-08-04</t>
+          <t>2406-06-04</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 7/16-20 x 3/4-16 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 7/16-20 x 9/16-18 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3/4-16 (female 37deg JIC)</t>
+          <t>9/16-18 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -1823,42 +1823,42 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2406-08-04</t>
+          <t>2406-06-04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2406-08-10</t>
+          <t>2406-06-05</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="C11" t="n">
-        <v>0.54271</v>
+        <v>0.39837</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4375</v>
+        <v>0.25</v>
       </c>
       <c r="F11" t="n">
-        <v>0.107</v>
+        <v>0.075</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3553</v>
+        <v>0.2606</v>
       </c>
       <c r="H11" t="n">
-        <v>0.386</v>
+        <v>0.213</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1114</v>
+        <v>0.0795</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1546</v>
+        <v>0.1135</v>
       </c>
       <c r="K11" t="n">
         <v>60</v>
@@ -1867,64 +1867,64 @@
         <v>37</v>
       </c>
       <c r="M11" t="n">
-        <v>0.875</v>
+        <v>0.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6213</v>
+        <v>0.4536</v>
       </c>
       <c r="P11" t="n">
-        <v>0.03866</v>
+        <v>0.02706</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01786</v>
+        <v>0.0125</v>
       </c>
       <c r="R11" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3775</v>
+        <v>0.2835</v>
       </c>
       <c r="T11" t="n">
-        <v>0.34117</v>
+        <v>0.25118</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3387</v>
+        <v>0.3117</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6823399999999999</v>
+        <v>0.50236</v>
       </c>
       <c r="W11" t="n">
-        <v>0.375</v>
+        <v>0.344</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.34117</v>
+        <v>0.25118</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.39</v>
+        <v>0.23</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.915</v>
+        <v>0.846</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2406-08-10</t>
+          <t>2406-06-05</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 7/8-14 x 3/4-16 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1/2-20 x 9/16-18 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>7/8-14</t>
+          <t>1/2-20</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>3/4-16 (female 37deg JIC)</t>
+          <t>9/16-18 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -1954,47 +1954,47 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.462 from the End A tip, inside the End A thread/groove zone (0.758); radial wall there min 0.163 at 0.758 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2406-08-10</t>
+          <t>2406-06-05</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2406-08-12</t>
+          <t>2406-06-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="C12" t="n">
-        <v>0.65241</v>
+        <v>0.39837</v>
       </c>
       <c r="D12" t="n">
-        <v>1.13</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.53125</v>
+        <v>0.28125</v>
       </c>
       <c r="F12" t="n">
-        <v>0.125</v>
+        <v>0.083</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3895</v>
+        <v>0.2515</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4715</v>
+        <v>0.2405</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1299</v>
+        <v>0.0898</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1851</v>
+        <v>0.1082</v>
       </c>
       <c r="K12" t="n">
         <v>60</v>
@@ -2003,64 +2003,64 @@
         <v>37</v>
       </c>
       <c r="M12" t="n">
-        <v>1.0625</v>
+        <v>0.5625</v>
       </c>
       <c r="N12" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7045</v>
+        <v>0.4495</v>
       </c>
       <c r="P12" t="n">
-        <v>0.04511</v>
+        <v>0.03007</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.02083</v>
+        <v>0.01389</v>
       </c>
       <c r="R12" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3775</v>
+        <v>0.2835</v>
       </c>
       <c r="T12" t="n">
-        <v>0.34117</v>
+        <v>0.25118</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3387</v>
+        <v>0.3117</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6823399999999999</v>
+        <v>0.50236</v>
       </c>
       <c r="W12" t="n">
-        <v>0.375</v>
+        <v>0.344</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.34117</v>
+        <v>0.25118</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.065</v>
+        <v>0.786</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2406-08-12</t>
+          <t>2406-06-06</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 1/16-12 x 3/4-16 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 9/16-18 x 9/16-18 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>1 1/16-12</t>
+          <t>9/16-18</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3/4-16 (female 37deg JIC)</t>
+          <t>9/16-18 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
@@ -2095,42 +2095,42 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2406-08-12</t>
+          <t>2406-06-06</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2406-08-16</t>
+          <t>2406-06-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.61</v>
+        <v>1.16</v>
       </c>
       <c r="C13" t="n">
-        <v>0.79674</v>
+        <v>0.46765</v>
       </c>
       <c r="D13" t="n">
-        <v>1.38</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.65625</v>
+        <v>0.375</v>
       </c>
       <c r="F13" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4365</v>
+        <v>0.2837</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5965</v>
+        <v>0.3295</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1292</v>
+        <v>0.0984</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1858</v>
+        <v>0.1546</v>
       </c>
       <c r="K13" t="n">
         <v>60</v>
@@ -2139,64 +2139,64 @@
         <v>37</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3125</v>
+        <v>0.75</v>
       </c>
       <c r="N13" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.5367</v>
       </c>
       <c r="P13" t="n">
-        <v>0.04511</v>
+        <v>0.03383</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.02083</v>
+        <v>0.01562</v>
       </c>
       <c r="R13" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3775</v>
+        <v>0.2835</v>
       </c>
       <c r="T13" t="n">
-        <v>0.34117</v>
+        <v>0.25118</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3387</v>
+        <v>0.3117</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6823399999999999</v>
+        <v>0.50236</v>
       </c>
       <c r="W13" t="n">
-        <v>0.375</v>
+        <v>0.344</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.34117</v>
+        <v>0.25118</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.61</v>
+        <v>1.16</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.235</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2406-08-16</t>
+          <t>2406-06-08</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 5/16-12 x 3/4-16 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 3/4-16 x 9/16-18 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>1 5/16-12</t>
+          <t>3/4-16</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>3/4-16 (female 37deg JIC)</t>
+          <t>9/16-18 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -2231,42 +2231,42 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2406-08-16</t>
+          <t>2406-06-08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2406-10-04</t>
+          <t>2406-06-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="C14" t="n">
-        <v>0.57735</v>
+        <v>0.54098</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>0.21875</v>
+        <v>0.4375</v>
       </c>
       <c r="F14" t="n">
-        <v>0.075</v>
+        <v>0.107</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2608</v>
+        <v>0.3553</v>
       </c>
       <c r="H14" t="n">
-        <v>0.182</v>
+        <v>0.386</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0795</v>
+        <v>0.1114</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1135</v>
+        <v>0.1546</v>
       </c>
       <c r="K14" t="n">
         <v>60</v>
@@ -2275,64 +2275,64 @@
         <v>37</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4375</v>
+        <v>0.875</v>
       </c>
       <c r="N14" t="n">
-        <v>0.05</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4538</v>
+        <v>0.6213</v>
       </c>
       <c r="P14" t="n">
-        <v>0.02706</v>
+        <v>0.03866</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0125</v>
+        <v>0.01786</v>
       </c>
       <c r="R14" t="n">
-        <v>0.05</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>0.44</v>
+        <v>0.2835</v>
       </c>
       <c r="T14" t="n">
-        <v>0.39884</v>
+        <v>0.25118</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4278</v>
+        <v>0.3117</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7976799999999999</v>
+        <v>0.50236</v>
       </c>
       <c r="W14" t="n">
-        <v>0.469</v>
+        <v>0.344</v>
       </c>
       <c r="X14" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.39884</v>
+        <v>0.25118</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.17</v>
+        <v>0.297</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.001</v>
+        <v>1.036</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2406-10-04</t>
+          <t>2406-06-10</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 7/16-20 x 7/8-14 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 7/8-14 x 9/16-18 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>7/16-20</t>
+          <t>7/8-14</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>7/8-14 (female 37deg JIC)</t>
+          <t>9/16-18 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -2357,52 +2357,52 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L23@DRIVE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-06-10 column 'L0 LGTH' = 1.38 (catalog_verified.json); OMi Items row 581: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-06-10 column 'C HEX' = 0.937 (catalog_verified.json); OMi Items row 581: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D3@BORE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-06-10 column 'B2 DRILL' = 0.297 (catalog_verified.json); OMi Items row 581: no dimension; no Air-Way row; equals the 2026-10-02 proposal; THDMAJ_A@DRIVE: gen_straight2 JIC[6] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, female end (first dash); catalog B1 9/16-18; equals the 2026-10-02 proposal; THDMAJ_B@DRIVE: gen_straight2 JIC[10] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male end (second dash); catalog B2 7/8-14; equals the 2026-10-02 proposal; JICB_RELIEFL@DRIVE: gen_straight2 JIC[10] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) RL; equals the 2026-10-02 proposal; JICB_THDZ@DRIVE: gen_straight2 JIC[10] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) TZ; equals the 2026-10-02 proposal; JICB_CONEDIA@DRIVE: gen_straight2 JIC[10] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) CD; equals the 2026-10-02 proposal; JICB_LANDL@DRIVE: gen_straight2 JIC[10] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) LL; equals the 2026-10-02 proposal; JICB_SEATL@DRIVE: gen_straight2 JIC[10] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) SL; equals the 2026-10-02 proposal; RELIEFANG@DRIVE: gen_straight2 end_JICM constant (60 deg relief ramp, every 2406 row); equals the 2026-10-02 proposal; SEATB@DRIVE: gen_straight2 end_JICM constant (37 deg flare seat, every 2406 row); equals the 2026-10-02 proposal; $PRP@EndA_Thread: gen_straight2 JIC[6] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text (format of the built 2406 rows); equals the 2026-10-02 proposal; $PRP@EndB_Thread: gen_straight2 JIC[10] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text; equals the 2026-10-02 proposal | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone; built rows of this table are Air-Way</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2406-10-04</t>
+          <t>2406-06-10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2406-10-06</t>
+          <t>2406-08-04</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="C15" t="n">
-        <v>0.57735</v>
+        <v>0.50807</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="E15" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="F15" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="K15" t="n">
         <v>60</v>
@@ -2411,64 +2411,64 @@
         <v>37</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="N15" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4495</v>
+        <v>0.4538</v>
       </c>
       <c r="P15" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="R15" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.44</v>
+        <v>0.3775</v>
       </c>
       <c r="T15" t="n">
-        <v>0.39884</v>
+        <v>0.34117</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4278</v>
+        <v>0.3387</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7976799999999999</v>
+        <v>0.6823399999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0.469</v>
+        <v>0.375</v>
       </c>
       <c r="X15" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.39884</v>
+        <v>0.34117</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.955</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2406-10-06</t>
+          <t>2406-08-04</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 9/16-18 x 7/8-14 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 7/16-20 x 3/4-16 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>9/16-18</t>
+          <t>7/16-20</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>7/8-14 (female 37deg JIC)</t>
+          <t>3/4-16 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
@@ -2503,24 +2503,24 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2406-10-06</t>
+          <t>2406-08-04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2406-10-08</t>
+          <t>2406-08-08</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1.41</v>
       </c>
       <c r="C16" t="n">
-        <v>0.57735</v>
+        <v>0.50518</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="E16" t="n">
         <v>0.375</v>
@@ -2565,46 +2565,46 @@
         <v>0.0625</v>
       </c>
       <c r="S16" t="n">
-        <v>0.44</v>
+        <v>0.3775</v>
       </c>
       <c r="T16" t="n">
-        <v>0.39884</v>
+        <v>0.34117</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4278</v>
+        <v>0.3387</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7976799999999999</v>
+        <v>0.6823399999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0.469</v>
+        <v>0.375</v>
       </c>
       <c r="X16" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.39884</v>
+        <v>0.34117</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="AA16" t="n">
         <v>1.41</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.39</v>
+        <v>0.391</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.9409999999999999</v>
+        <v>1.035</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2406-10-08</t>
+          <t>2406-08-08</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 3/4-16 x 7/8-14 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 3/4-16 x 3/4-16 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>7/8-14 (female 37deg JIC)</t>
+          <t>3/4-16 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -2629,52 +2629,52 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L23@DRIVE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-08-08 column 'L0 LGTH' = 1.41 (catalog_verified.json); OMi Items row 585: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-08-08 column 'C HEX' = 0.875 (catalog_verified.json); OMi Items row 585: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D3@BORE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-08-08 column 'B2 DRILL' = 0.391 (catalog_verified.json); OMi Items row 585: no dimension; no Air-Way row; equals the 2026-10-02 proposal; THDMAJ_A@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, female end (first dash); catalog B1 3/4-16; equals the 2026-10-02 proposal; THDMAJ_B@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male end (second dash); catalog B2 3/4-16; equals the 2026-10-02 proposal; JICB_RELIEFL@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) RL; equals the 2026-10-02 proposal; JICB_THDZ@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) TZ; equals the 2026-10-02 proposal; JICB_CONEDIA@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) CD; equals the 2026-10-02 proposal; JICB_LANDL@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) LL; equals the 2026-10-02 proposal; JICB_SEATL@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) SL; equals the 2026-10-02 proposal; RELIEFANG@DRIVE: gen_straight2 end_JICM constant (60 deg relief ramp, every 2406 row); equals the 2026-10-02 proposal; SEATB@DRIVE: gen_straight2 end_JICM constant (37 deg flare seat, every 2406 row); equals the 2026-10-02 proposal; $PRP@EndA_Thread: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text (format of the built 2406 rows); equals the 2026-10-02 proposal; $PRP@EndB_Thread: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text; equals the 2026-10-02 proposal | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone; built rows of this table are Air-Way</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2406-10-08</t>
+          <t>2406-08-08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2406-10-12</t>
+          <t>2406-08-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="C17" t="n">
-        <v>0.65241</v>
+        <v>0.54271</v>
       </c>
       <c r="D17" t="n">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="F17" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="K17" t="n">
         <v>60</v>
@@ -2683,64 +2683,64 @@
         <v>37</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="N17" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7045</v>
+        <v>0.6213</v>
       </c>
       <c r="P17" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="R17" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>0.44</v>
+        <v>0.3775</v>
       </c>
       <c r="T17" t="n">
-        <v>0.39884</v>
+        <v>0.34117</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4278</v>
+        <v>0.3387</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7976799999999999</v>
+        <v>0.6823399999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>0.469</v>
+        <v>0.375</v>
       </c>
       <c r="X17" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.39884</v>
+        <v>0.34117</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.48</v>
+        <v>0.39</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.021</v>
+        <v>0.915</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2406-10-12</t>
+          <t>2406-08-10</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 1/16-12 x 7/8-14 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 7/8-14 x 3/4-16 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>1 1/16-12</t>
+          <t>7/8-14</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>7/8-14 (female 37deg JIC)</t>
+          <t>3/4-16 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
@@ -2770,47 +2770,47 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.492 from the End A tip, inside the End A thread/groove zone (0.864); radial wall there min 0.191 at 0.864 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.462 from the End A tip, inside the End A thread/groove zone (0.758); radial wall there min 0.163 at 0.758 from the tip (OK)</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2406-10-12</t>
+          <t>2406-08-10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2406-12-06</t>
+          <t>2406-08-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.65241</v>
       </c>
       <c r="D18" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="E18" t="n">
-        <v>0.28125</v>
+        <v>0.53125</v>
       </c>
       <c r="F18" t="n">
-        <v>0.083</v>
+        <v>0.125</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2515</v>
+        <v>0.3895</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2405</v>
+        <v>0.4715</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0898</v>
+        <v>0.1299</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1082</v>
+        <v>0.1851</v>
       </c>
       <c r="K18" t="n">
         <v>60</v>
@@ -2819,64 +2819,64 @@
         <v>37</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5625</v>
+        <v>1.0625</v>
       </c>
       <c r="N18" t="n">
-        <v>0.05556</v>
+        <v>0.08333</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4495</v>
+        <v>0.7045</v>
       </c>
       <c r="P18" t="n">
-        <v>0.03007</v>
+        <v>0.04511</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.01389</v>
+        <v>0.02083</v>
       </c>
       <c r="R18" t="n">
-        <v>0.05556</v>
+        <v>0.08333</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5335</v>
+        <v>0.3775</v>
       </c>
       <c r="T18" t="n">
-        <v>0.48614</v>
+        <v>0.34117</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4526</v>
+        <v>0.3387</v>
       </c>
       <c r="V18" t="n">
-        <v>0.97228</v>
+        <v>0.6823399999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="X18" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.48614</v>
+        <v>0.34117</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.96</v>
+        <v>1.065</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2406-12-06</t>
+          <t>2406-08-12</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 9/16-18 x 1 1/16-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 1/16-12 x 3/4-16 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2886,12 +2886,12 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>9/16-18</t>
+          <t>1 1/16-12</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female 37deg JIC)</t>
+          <t>3/4-16 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
@@ -2906,47 +2906,47 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.315 from the End A tip, inside the End A thread/groove zone (0.556); radial wall there min 0.059 at 0.556 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2406-12-06</t>
+          <t>2406-08-12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2406-12-08</t>
+          <t>2406-08-16</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.79674</v>
       </c>
       <c r="D19" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="E19" t="n">
-        <v>0.375</v>
+        <v>0.65625</v>
       </c>
       <c r="F19" t="n">
-        <v>0.094</v>
+        <v>0.125</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2837</v>
+        <v>0.4365</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3295</v>
+        <v>0.5965</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0984</v>
+        <v>0.1292</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1546</v>
+        <v>0.1858</v>
       </c>
       <c r="K19" t="n">
         <v>60</v>
@@ -2955,64 +2955,64 @@
         <v>37</v>
       </c>
       <c r="M19" t="n">
-        <v>0.75</v>
+        <v>1.3125</v>
       </c>
       <c r="N19" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.7514999999999999</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.3775</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.6823399999999999</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="X19" t="n">
         <v>0.0625</v>
       </c>
-      <c r="O19" t="n">
-        <v>0.5367</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.03383</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.01562</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.5335</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.48614</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.4526</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0.97228</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0.08333</v>
-      </c>
       <c r="Y19" t="n">
-        <v>0.48614</v>
+        <v>0.34117</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AB19" t="n">
         <v>0.39</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.06</v>
+        <v>1.235</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2406-12-08</t>
+          <t>2406-08-16</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 3/4-16 x 1 1/16-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 5/16-12 x 3/4-16 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>3/4-16</t>
+          <t>1 5/16-12</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female 37deg JIC)</t>
+          <t>3/4-16 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
@@ -3047,42 +3047,42 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2406-12-08</t>
+          <t>2406-08-16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2406-12-10</t>
+          <t>2406-10-04</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.57735</v>
       </c>
       <c r="D20" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4375</v>
+        <v>0.21875</v>
       </c>
       <c r="F20" t="n">
-        <v>0.107</v>
+        <v>0.075</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3553</v>
+        <v>0.2608</v>
       </c>
       <c r="H20" t="n">
-        <v>0.386</v>
+        <v>0.182</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1114</v>
+        <v>0.0795</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1546</v>
+        <v>0.1135</v>
       </c>
       <c r="K20" t="n">
         <v>60</v>
@@ -3091,64 +3091,64 @@
         <v>37</v>
       </c>
       <c r="M20" t="n">
-        <v>0.875</v>
+        <v>0.4375</v>
       </c>
       <c r="N20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.4538</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.02706</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.4278</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.7976799999999999</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="X20" t="n">
         <v>0.07142999999999999</v>
       </c>
-      <c r="O20" t="n">
-        <v>0.6213</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.03866</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.01786</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.07142999999999999</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.5335</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.48614</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.4526</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0.97228</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0.08333</v>
-      </c>
       <c r="Y20" t="n">
-        <v>0.48614</v>
+        <v>0.39884</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.48</v>
+        <v>0.17</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.14</v>
+        <v>1.001</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2406-12-10</t>
+          <t>2406-10-04</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 7/8-14 x 1 1/16-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 7/16-20 x 7/8-14 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>7/8-14</t>
+          <t>7/16-20</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female 37deg JIC)</t>
+          <t>7/8-14 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
@@ -3183,42 +3183,42 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2406-12-10</t>
+          <t>2406-10-04</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2406-12-16</t>
+          <t>2406-10-06</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="C21" t="n">
-        <v>0.79674</v>
+        <v>0.57735</v>
       </c>
       <c r="D21" t="n">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.65625</v>
+        <v>0.28125</v>
       </c>
       <c r="F21" t="n">
-        <v>0.125</v>
+        <v>0.083</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4365</v>
+        <v>0.2515</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5965</v>
+        <v>0.2405</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1292</v>
+        <v>0.0898</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1858</v>
+        <v>0.1082</v>
       </c>
       <c r="K21" t="n">
         <v>60</v>
@@ -3227,64 +3227,64 @@
         <v>37</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3125</v>
+        <v>0.5625</v>
       </c>
       <c r="N21" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.4495</v>
       </c>
       <c r="P21" t="n">
-        <v>0.04511</v>
+        <v>0.03007</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.02083</v>
+        <v>0.01389</v>
       </c>
       <c r="R21" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5335</v>
+        <v>0.44</v>
       </c>
       <c r="T21" t="n">
-        <v>0.48614</v>
+        <v>0.39884</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4526</v>
+        <v>0.4278</v>
       </c>
       <c r="V21" t="n">
-        <v>0.97228</v>
+        <v>0.7976799999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5</v>
+        <v>0.469</v>
       </c>
       <c r="X21" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.48614</v>
+        <v>0.39884</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.61</v>
+        <v>0.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.11</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2406-12-16</t>
+          <t>2406-10-06</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 5/16-12 x 1 1/16-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 9/16-18 x 7/8-14 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>1 5/16-12</t>
+          <t>9/16-18</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female 37deg JIC)</t>
+          <t>7/8-14 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
@@ -3314,47 +3314,47 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.465 from the End A tip, inside the End A thread/groove zone (0.911); radial wall there min 0.260 at 0.911 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2406-12-16</t>
+          <t>2406-10-06</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2406-12-20</t>
+          <t>2406-10-08</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.71</v>
+        <v>1.41</v>
       </c>
       <c r="C22" t="n">
-        <v>0.97572</v>
+        <v>0.57735</v>
       </c>
       <c r="D22" t="n">
-        <v>1.69</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8125</v>
+        <v>0.375</v>
       </c>
       <c r="F22" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4316</v>
+        <v>0.2837</v>
       </c>
       <c r="H22" t="n">
-        <v>0.753</v>
+        <v>0.3295</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1288</v>
+        <v>0.0984</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2382</v>
+        <v>0.1546</v>
       </c>
       <c r="K22" t="n">
         <v>60</v>
@@ -3363,64 +3363,64 @@
         <v>37</v>
       </c>
       <c r="M22" t="n">
-        <v>1.625</v>
+        <v>0.75</v>
       </c>
       <c r="N22" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7986</v>
+        <v>0.5367</v>
       </c>
       <c r="P22" t="n">
-        <v>0.04511</v>
+        <v>0.03383</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.02083</v>
+        <v>0.01562</v>
       </c>
       <c r="R22" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5335</v>
+        <v>0.44</v>
       </c>
       <c r="T22" t="n">
-        <v>0.48614</v>
+        <v>0.39884</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4526</v>
+        <v>0.4278</v>
       </c>
       <c r="V22" t="n">
-        <v>0.97228</v>
+        <v>0.7976799999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5</v>
+        <v>0.469</v>
       </c>
       <c r="X22" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.48614</v>
+        <v>0.39884</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.71</v>
+        <v>1.41</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.61</v>
+        <v>0.39</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.21</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2406-12-20</t>
+          <t>2406-10-08</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 5/8-12 x 1 1/16-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 3/4-16 x 7/8-14 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>1 5/8-12</t>
+          <t>3/4-16</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female 37deg JIC)</t>
+          <t>7/8-14 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
@@ -3455,42 +3455,42 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2406-12-20</t>
+          <t>2406-10-08</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2406-14-10</t>
+          <t>2406-10-12</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="C23" t="n">
-        <v>0.79674</v>
+        <v>0.65241</v>
       </c>
       <c r="D23" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4375</v>
+        <v>0.53125</v>
       </c>
       <c r="F23" t="n">
-        <v>0.107</v>
+        <v>0.125</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3553</v>
+        <v>0.3895</v>
       </c>
       <c r="H23" t="n">
-        <v>0.386</v>
+        <v>0.4715</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1114</v>
+        <v>0.1299</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1546</v>
+        <v>0.1851</v>
       </c>
       <c r="K23" t="n">
         <v>60</v>
@@ -3499,64 +3499,64 @@
         <v>37</v>
       </c>
       <c r="M23" t="n">
-        <v>0.875</v>
+        <v>1.0625</v>
       </c>
       <c r="N23" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.7045</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.4278</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.7976799999999999</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="X23" t="n">
         <v>0.07142999999999999</v>
       </c>
-      <c r="O23" t="n">
-        <v>0.6213</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.03866</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.01786</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.07142999999999999</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.5965</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.54864</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0.4831</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.09728</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0.08333</v>
-      </c>
       <c r="Y23" t="n">
-        <v>0.54864</v>
+        <v>0.39884</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.59375</v>
+        <v>0.4375</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AB23" t="n">
         <v>0.48</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.199</v>
+        <v>1.021</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2406-14-10</t>
+          <t>2406-10-12</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 7/8-14 x 1 3/16-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 1/16-12 x 7/8-14 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>7/8-14</t>
+          <t>1 1/16-12</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1 3/16-12 (female 37deg JIC)</t>
+          <t>7/8-14 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
@@ -3586,47 +3586,47 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.492 from the End A tip, inside the End A thread/groove zone (0.864); radial wall there min 0.191 at 0.864 from the tip (OK)</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2406-14-10</t>
+          <t>2406-10-12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2406-16-06</t>
+          <t>2406-10-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="C24" t="n">
-        <v>0.86603</v>
+        <v>0.79386</v>
       </c>
       <c r="D24" t="n">
-        <v>1.5</v>
+        <v>1.375</v>
       </c>
       <c r="E24" t="n">
-        <v>0.28125</v>
+        <v>0.65625</v>
       </c>
       <c r="F24" t="n">
-        <v>0.083</v>
+        <v>0.125</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2515</v>
+        <v>0.4365</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2405</v>
+        <v>0.5965</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0898</v>
+        <v>0.1292</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1082</v>
+        <v>0.1858</v>
       </c>
       <c r="K24" t="n">
         <v>60</v>
@@ -3635,64 +3635,64 @@
         <v>37</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5625</v>
+        <v>1.3125</v>
       </c>
       <c r="N24" t="n">
-        <v>0.05556</v>
+        <v>0.08333</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4495</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>0.03007</v>
+        <v>0.04511</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.01389</v>
+        <v>0.02083</v>
       </c>
       <c r="R24" t="n">
-        <v>0.05556</v>
+        <v>0.08333</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6585</v>
+        <v>0.44</v>
       </c>
       <c r="T24" t="n">
-        <v>0.61114</v>
+        <v>0.39884</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.4278</v>
       </c>
       <c r="V24" t="n">
-        <v>1.22228</v>
+        <v>0.7976799999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.469</v>
       </c>
       <c r="X24" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.61114</v>
+        <v>0.39884</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.65625</v>
+        <v>0.4375</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.3</v>
+        <v>0.484</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.087</v>
+        <v>1.291</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>2406-16-06</t>
+          <t>2406-10-16</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 9/16-18 x 1 5/16-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 5/16-12 x 7/8-14 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>9/16-18</t>
+          <t>1 5/16-12</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female 37deg JIC)</t>
+          <t>7/8-14 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
@@ -3717,52 +3717,52 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L23@DRIVE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-10-16 column 'L0 LGTH' = 1.76 (catalog_verified.json); OMi Items row 594: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-10-16 column 'C HEX' = 1.375 (catalog_verified.json); OMi Items row 594: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D3@BORE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-10-16 column 'B2 DRILL' = 0.484 (catalog_verified.json); OMi Items row 594: no dimension; no Air-Way row; equals the 2026-10-02 proposal; THDMAJ_A@DRIVE: gen_straight2 JIC[10] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, female end (first dash); catalog B1 7/8-14; equals the 2026-10-02 proposal; THDMAJ_B@DRIVE: gen_straight2 JIC[16] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male end (second dash); catalog B2 1-5/16-12; equals the 2026-10-02 proposal; JICB_RELIEFL@DRIVE: gen_straight2 JIC[16] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) RL; equals the 2026-10-02 proposal; JICB_THDZ@DRIVE: gen_straight2 JIC[16] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) TZ; equals the 2026-10-02 proposal; JICB_CONEDIA@DRIVE: gen_straight2 JIC[16] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) CD; equals the 2026-10-02 proposal; JICB_LANDL@DRIVE: gen_straight2 JIC[16] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) LL; equals the 2026-10-02 proposal; JICB_SEATL@DRIVE: gen_straight2 JIC[16] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) SL; equals the 2026-10-02 proposal; RELIEFANG@DRIVE: gen_straight2 end_JICM constant (60 deg relief ramp, every 2406 row); equals the 2026-10-02 proposal; SEATB@DRIVE: gen_straight2 end_JICM constant (37 deg flare seat, every 2406 row); equals the 2026-10-02 proposal; $PRP@EndA_Thread: gen_straight2 JIC[10] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text (format of the built 2406 rows); equals the 2026-10-02 proposal; $PRP@EndB_Thread: gen_straight2 JIC[16] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text; equals the 2026-10-02 proposal | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.276 from the End A tip, inside the End A thread/groove zone (0.556); radial wall there min 0.029 at 0.556 from the tip (THIN)</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone; built rows of this table are Air-Way</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2406-16-06</t>
+          <t>2406-10-16</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2406-16-08</t>
+          <t>2406-12-04</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="C25" t="n">
-        <v>0.86603</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="E25" t="n">
-        <v>0.375</v>
+        <v>0.21875</v>
       </c>
       <c r="F25" t="n">
-        <v>0.094</v>
+        <v>0.075</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2837</v>
+        <v>0.2608</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3295</v>
+        <v>0.182</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0984</v>
+        <v>0.0795</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1546</v>
+        <v>0.1135</v>
       </c>
       <c r="K25" t="n">
         <v>60</v>
@@ -3771,64 +3771,64 @@
         <v>37</v>
       </c>
       <c r="M25" t="n">
-        <v>0.75</v>
+        <v>0.4375</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0625</v>
+        <v>0.05</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5367</v>
+        <v>0.4538</v>
       </c>
       <c r="P25" t="n">
-        <v>0.03383</v>
+        <v>0.02706</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.01562</v>
+        <v>0.0125</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0625</v>
+        <v>0.05</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6585</v>
+        <v>0.5335</v>
       </c>
       <c r="T25" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.4526</v>
       </c>
       <c r="V25" t="n">
-        <v>1.22228</v>
+        <v>0.97228</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="X25" t="n">
         <v>0.08333</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.39</v>
+        <v>0.172</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.157</v>
+        <v>1</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>2406-16-08</t>
+          <t>2406-12-04</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 3/4-16 x 1 5/16-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 7/16-20 x 1 1/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>3/4-16</t>
+          <t>7/16-20</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female 37deg JIC)</t>
+          <t>1 1/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
@@ -3853,52 +3853,52 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L23@DRIVE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-12-04 column 'L0 LGTH' = 1.50 (catalog_verified.json); OMi Items row 595: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-12-04 column 'C HEX' = 1.250 (catalog_verified.json); OMi Items row 595: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D3@BORE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-12-04 column 'B2 DRILL' = 0.172 (catalog_verified.json); OMi Items row 595: no dimension; no Air-Way row; equals the 2026-10-02 proposal; THDMAJ_A@DRIVE: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, female end (first dash); catalog B1 1-1/16-12; equals the 2026-10-02 proposal; THDMAJ_B@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male end (second dash); catalog B2 7/16-20; equals the 2026-10-02 proposal; JICB_RELIEFL@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) RL; equals the 2026-10-02 proposal; JICB_THDZ@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) TZ; equals the 2026-10-02 proposal; JICB_CONEDIA@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) CD; equals the 2026-10-02 proposal; JICB_LANDL@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) LL; equals the 2026-10-02 proposal; JICB_SEATL@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) SL; equals the 2026-10-02 proposal; RELIEFANG@DRIVE: gen_straight2 end_JICM constant (60 deg relief ramp, every 2406 row); equals the 2026-10-02 proposal; SEATB@DRIVE: gen_straight2 end_JICM constant (37 deg flare seat, every 2406 row); equals the 2026-10-02 proposal; $PRP@EndA_Thread: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text (format of the built 2406 rows); equals the 2026-10-02 proposal; $PRP@EndB_Thread: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text; equals the 2026-10-02 proposal | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.346 from the End A tip, inside the End A thread/groove zone (0.657); radial wall there min 0.095 at 0.657 from the tip (OK)</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone; built rows of this table are Air-Way | female port reaches 0.355 from the End A tip, inside the End A thread/groove zone (0.550); radial wall there min 0.035 at 0.550 from the tip (OK)</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2406-16-08</t>
+          <t>2406-12-04</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2406-16-10</t>
+          <t>2406-12-06</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.79</v>
+        <v>1.46</v>
       </c>
       <c r="C26" t="n">
-        <v>0.86603</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="F26" t="n">
-        <v>0.107</v>
+        <v>0.083</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3553</v>
+        <v>0.2515</v>
       </c>
       <c r="H26" t="n">
-        <v>0.386</v>
+        <v>0.2405</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1114</v>
+        <v>0.0898</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="K26" t="n">
         <v>60</v>
@@ -3907,64 +3907,64 @@
         <v>37</v>
       </c>
       <c r="M26" t="n">
-        <v>0.875</v>
+        <v>0.5625</v>
       </c>
       <c r="N26" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="O26" t="n">
-        <v>0.6213</v>
+        <v>0.4495</v>
       </c>
       <c r="P26" t="n">
-        <v>0.03866</v>
+        <v>0.03007</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.01786</v>
+        <v>0.01389</v>
       </c>
       <c r="R26" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6585</v>
+        <v>0.5335</v>
       </c>
       <c r="T26" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="U26" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.4526</v>
       </c>
       <c r="V26" t="n">
-        <v>1.22228</v>
+        <v>0.97228</v>
       </c>
       <c r="W26" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="X26" t="n">
         <v>0.08333</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.79</v>
+        <v>1.46</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.227</v>
+        <v>0.96</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>2406-16-10</t>
+          <t>2406-12-06</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 7/8-14 x 1 5/16-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 9/16-18 x 1 1/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>7/8-14</t>
+          <t>9/16-18</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female 37deg JIC)</t>
+          <t>1 1/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
@@ -3994,47 +3994,47 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.416 from the End A tip, inside the End A thread/groove zone (0.758); radial wall there min 0.128 at 0.758 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.315 from the End A tip, inside the End A thread/groove zone (0.556); radial wall there min 0.059 at 0.556 from the tip (OK)</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2406-16-10</t>
+          <t>2406-12-06</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2406-16-12</t>
+          <t>2406-12-08</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="C27" t="n">
-        <v>0.86603</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="E27" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="F27" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3895</v>
+        <v>0.2837</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4715</v>
+        <v>0.3295</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1299</v>
+        <v>0.0984</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="K27" t="n">
         <v>60</v>
@@ -4043,64 +4043,64 @@
         <v>37</v>
       </c>
       <c r="M27" t="n">
-        <v>1.0625</v>
+        <v>0.75</v>
       </c>
       <c r="N27" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="O27" t="n">
-        <v>0.7045</v>
+        <v>0.5367</v>
       </c>
       <c r="P27" t="n">
-        <v>0.04511</v>
+        <v>0.03383</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.02083</v>
+        <v>0.01562</v>
       </c>
       <c r="R27" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="S27" t="n">
-        <v>0.6585</v>
+        <v>0.5335</v>
       </c>
       <c r="T27" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.4526</v>
       </c>
       <c r="V27" t="n">
-        <v>1.22228</v>
+        <v>0.97228</v>
       </c>
       <c r="W27" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="X27" t="n">
         <v>0.08333</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.61</v>
+        <v>0.39</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.257</v>
+        <v>1.06</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>2406-16-12</t>
+          <t>2406-12-08</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 1/16-12 x 1 5/16-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 3/4-16 x 1 1/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>1 1/16-12</t>
+          <t>3/4-16</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female 37deg JIC)</t>
+          <t>1 1/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
@@ -4130,47 +4130,47 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.446 from the End A tip, inside the End A thread/groove zone (0.864); radial wall there min 0.157 at 0.864 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2406-16-12</t>
+          <t>2406-12-08</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2406-16-14</t>
+          <t>2406-12-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="C28" t="n">
-        <v>0.86603</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="E28" t="n">
-        <v>0.59375</v>
+        <v>0.4375</v>
       </c>
       <c r="F28" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4155</v>
+        <v>0.3553</v>
       </c>
       <c r="H28" t="n">
-        <v>0.534</v>
+        <v>0.386</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1292</v>
+        <v>0.1114</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1858</v>
+        <v>0.1546</v>
       </c>
       <c r="K28" t="n">
         <v>60</v>
@@ -4179,64 +4179,64 @@
         <v>37</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1875</v>
+        <v>0.875</v>
       </c>
       <c r="N28" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>0.7305</v>
+        <v>0.6213</v>
       </c>
       <c r="P28" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="R28" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>0.6585</v>
+        <v>0.5335</v>
       </c>
       <c r="T28" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="U28" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.4526</v>
       </c>
       <c r="V28" t="n">
-        <v>1.22228</v>
+        <v>0.97228</v>
       </c>
       <c r="W28" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="X28" t="n">
         <v>0.08333</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.72</v>
+        <v>0.48</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.297</v>
+        <v>1.14</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>2406-16-14</t>
+          <t>2406-12-10</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 3/16-12 x 1 5/16-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 7/8-14 x 1 1/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -4246,12 +4246,12 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>1 3/16-12</t>
+          <t>7/8-14</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female 37deg JIC)</t>
+          <t>1 1/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
@@ -4271,42 +4271,42 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2406-16-14</t>
+          <t>2406-12-10</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2406-16-20</t>
+          <t>2406-12-12</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="C29" t="n">
-        <v>0.97572</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>1.69</v>
+        <v>1.25</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="F29" t="n">
         <v>0.125</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4316</v>
+        <v>0.3895</v>
       </c>
       <c r="H29" t="n">
-        <v>0.753</v>
+        <v>0.4715</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1288</v>
+        <v>0.1299</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2382</v>
+        <v>0.1851</v>
       </c>
       <c r="K29" t="n">
         <v>60</v>
@@ -4315,13 +4315,13 @@
         <v>37</v>
       </c>
       <c r="M29" t="n">
-        <v>1.625</v>
+        <v>1.0625</v>
       </c>
       <c r="N29" t="n">
         <v>0.08333</v>
       </c>
       <c r="O29" t="n">
-        <v>0.7986</v>
+        <v>0.7045</v>
       </c>
       <c r="P29" t="n">
         <v>0.04511</v>
@@ -4333,46 +4333,46 @@
         <v>0.08333</v>
       </c>
       <c r="S29" t="n">
-        <v>0.6585</v>
+        <v>0.5335</v>
       </c>
       <c r="T29" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="U29" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.4526</v>
       </c>
       <c r="V29" t="n">
-        <v>1.22228</v>
+        <v>0.97228</v>
       </c>
       <c r="W29" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="X29" t="n">
         <v>0.08333</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.84</v>
+        <v>0.609</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.147</v>
+        <v>1.27</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>2406-16-20</t>
+          <t>2406-12-12</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 5/8-12 x 1 5/16-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 1/16-12 x 1 1/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>1 5/8-12</t>
+          <t>1 1/16-12</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female 37deg JIC)</t>
+          <t>1 1/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
@@ -4397,52 +4397,52 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L23@DRIVE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-12-12 column 'L0 LGTH' = 1.77 (catalog_verified.json); OMi Items row 599: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-12-12 column 'C HEX' = 1.250 (catalog_verified.json); OMi Items row 599: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D3@BORE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-12-12 column 'B2 DRILL' = 0.609 (catalog_verified.json); OMi Items row 599: no dimension; no Air-Way row; equals the 2026-10-02 proposal; THDMAJ_A@DRIVE: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, female end (first dash); catalog B1 1-1/16-12; equals the 2026-10-02 proposal; THDMAJ_B@DRIVE: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male end (second dash); catalog B2 1-1/16-12; equals the 2026-10-02 proposal; JICB_RELIEFL@DRIVE: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) RL; equals the 2026-10-02 proposal; JICB_THDZ@DRIVE: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) TZ; equals the 2026-10-02 proposal; JICB_CONEDIA@DRIVE: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) CD; equals the 2026-10-02 proposal; JICB_LANDL@DRIVE: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) LL; equals the 2026-10-02 proposal; JICB_SEATL@DRIVE: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) SL; equals the 2026-10-02 proposal; RELIEFANG@DRIVE: gen_straight2 end_JICM constant (60 deg relief ramp, every 2406 row); equals the 2026-10-02 proposal; SEATB@DRIVE: gen_straight2 end_JICM constant (37 deg flare seat, every 2406 row); equals the 2026-10-02 proposal; $PRP@EndA_Thread: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text (format of the built 2406 rows); equals the 2026-10-02 proposal; $PRP@EndB_Thread: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text; equals the 2026-10-02 proposal | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.336 from the End A tip, inside the End A thread/groove zone (0.958); radial wall there min 0.284 at 0.958 from the tip (OK)</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone; built rows of this table are Air-Way</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>2406-16-20</t>
+          <t>2406-12-12</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2406-16-24</t>
+          <t>2406-12-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="C30" t="n">
-        <v>1.1547</v>
+        <v>0.79674</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="F30" t="n">
         <v>0.125</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5454</v>
+        <v>0.4365</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.5965</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1298</v>
+        <v>0.1292</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2482</v>
+        <v>0.1858</v>
       </c>
       <c r="K30" t="n">
         <v>60</v>
@@ -4451,13 +4451,13 @@
         <v>37</v>
       </c>
       <c r="M30" t="n">
-        <v>1.875</v>
+        <v>1.3125</v>
       </c>
       <c r="N30" t="n">
         <v>0.08333</v>
       </c>
       <c r="O30" t="n">
-        <v>0.9234</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="P30" t="n">
         <v>0.04511</v>
@@ -4469,46 +4469,46 @@
         <v>0.08333</v>
       </c>
       <c r="S30" t="n">
-        <v>0.6585</v>
+        <v>0.5335</v>
       </c>
       <c r="T30" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="U30" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.4526</v>
       </c>
       <c r="V30" t="n">
-        <v>1.22228</v>
+        <v>0.97228</v>
       </c>
       <c r="W30" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="X30" t="n">
         <v>0.08333</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.247</v>
+        <v>1.11</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>2406-16-24</t>
+          <t>2406-12-16</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 7/8-12 x 1 5/16-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 5/16-12 x 1 1/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>1 7/8-12</t>
+          <t>1 5/16-12</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female 37deg JIC)</t>
+          <t>1 1/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
@@ -4538,47 +4538,47 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.436 from the End A tip, inside the End A thread/groove zone (1.083); radial wall there min 0.390 at 1.083 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.465 from the End A tip, inside the End A thread/groove zone (0.911); radial wall there min 0.260 at 0.911 from the tip (OK)</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>2406-16-24</t>
+          <t>2406-12-16</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2406-20-08</t>
+          <t>2406-12-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="C31" t="n">
-        <v>1.1547</v>
+        <v>0.97572</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="E31" t="n">
-        <v>0.375</v>
+        <v>0.8125</v>
       </c>
       <c r="F31" t="n">
-        <v>0.094</v>
+        <v>0.125</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2837</v>
+        <v>0.4316</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3295</v>
+        <v>0.753</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0984</v>
+        <v>0.1288</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1546</v>
+        <v>0.2382</v>
       </c>
       <c r="K31" t="n">
         <v>60</v>
@@ -4587,64 +4587,64 @@
         <v>37</v>
       </c>
       <c r="M31" t="n">
-        <v>0.75</v>
+        <v>1.625</v>
       </c>
       <c r="N31" t="n">
-        <v>0.0625</v>
+        <v>0.08333</v>
       </c>
       <c r="O31" t="n">
-        <v>0.5367</v>
+        <v>0.7986</v>
       </c>
       <c r="P31" t="n">
-        <v>0.03383</v>
+        <v>0.04511</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.01562</v>
+        <v>0.02083</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0625</v>
+        <v>0.08333</v>
       </c>
       <c r="S31" t="n">
-        <v>0.835</v>
+        <v>0.5335</v>
       </c>
       <c r="T31" t="n">
-        <v>0.76739</v>
+        <v>0.48614</v>
       </c>
       <c r="U31" t="n">
-        <v>0.4954</v>
+        <v>0.4526</v>
       </c>
       <c r="V31" t="n">
-        <v>1.53478</v>
+        <v>0.97228</v>
       </c>
       <c r="W31" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="X31" t="n">
         <v>0.08333</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.76739</v>
+        <v>0.48614</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.39</v>
+        <v>0.61</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.277</v>
+        <v>1.21</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>2406-20-08</t>
+          <t>2406-12-20</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 3/4-16 x 1 5/8-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 5/8-12 x 1 1/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>3/4-16</t>
+          <t>1 5/8-12</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>1 5/8-12 (female 37deg JIC)</t>
+          <t>1 1/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
@@ -4674,29 +4674,29 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.259 from the End A tip, inside the End A thread/groove zone (0.657); radial wall there min 0.029 at 0.657 from the tip (THIN)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>2406-20-08</t>
+          <t>2406-12-20</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2406-20-10</t>
+          <t>2406-14-10</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="C32" t="n">
-        <v>1.1547</v>
+        <v>0.79674</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="E32" t="n">
         <v>0.4375</v>
@@ -4741,46 +4741,46 @@
         <v>0.07142999999999999</v>
       </c>
       <c r="S32" t="n">
-        <v>0.835</v>
+        <v>0.5965</v>
       </c>
       <c r="T32" t="n">
-        <v>0.76739</v>
+        <v>0.54864</v>
       </c>
       <c r="U32" t="n">
-        <v>0.4954</v>
+        <v>0.4831</v>
       </c>
       <c r="V32" t="n">
-        <v>1.53478</v>
+        <v>1.09728</v>
       </c>
       <c r="W32" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.531</v>
       </c>
       <c r="X32" t="n">
         <v>0.08333</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.76739</v>
+        <v>0.54864</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.8125</v>
+        <v>0.59375</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AB32" t="n">
         <v>0.48</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.347</v>
+        <v>1.199</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>2406-20-10</t>
+          <t>2406-14-10</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 7/8-14 x 1 5/8-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 7/8-14 x 1 3/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>1 5/8-12 (female 37deg JIC)</t>
+          <t>1 3/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
@@ -4810,47 +4810,47 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.329 from the End A tip, inside the End A thread/groove zone (0.758); radial wall there min 0.062 at 0.758 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>2406-20-10</t>
+          <t>2406-14-10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2406-20-24</t>
+          <t>2406-16-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.14</v>
+        <v>1.65</v>
       </c>
       <c r="C33" t="n">
-        <v>1.1547</v>
+        <v>0.86603</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9375</v>
+        <v>0.28125</v>
       </c>
       <c r="F33" t="n">
-        <v>0.125</v>
+        <v>0.083</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5454</v>
+        <v>0.2515</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.2405</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1298</v>
+        <v>0.0898</v>
       </c>
       <c r="J33" t="n">
-        <v>0.2482</v>
+        <v>0.1082</v>
       </c>
       <c r="K33" t="n">
         <v>60</v>
@@ -4859,34 +4859,34 @@
         <v>37</v>
       </c>
       <c r="M33" t="n">
-        <v>1.875</v>
+        <v>0.5625</v>
       </c>
       <c r="N33" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="O33" t="n">
-        <v>0.9234</v>
+        <v>0.4495</v>
       </c>
       <c r="P33" t="n">
-        <v>0.04511</v>
+        <v>0.03007</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.02083</v>
+        <v>0.01389</v>
       </c>
       <c r="R33" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="S33" t="n">
-        <v>0.835</v>
+        <v>0.6585</v>
       </c>
       <c r="T33" t="n">
-        <v>0.76739</v>
+        <v>0.61114</v>
       </c>
       <c r="U33" t="n">
-        <v>0.4954</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="V33" t="n">
-        <v>1.53478</v>
+        <v>1.22228</v>
       </c>
       <c r="W33" t="n">
         <v>0.5629999999999999</v>
@@ -4895,28 +4895,28 @@
         <v>0.08333</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.76739</v>
+        <v>0.61114</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.14</v>
+        <v>1.65</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.08</v>
+        <v>0.3</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.577</v>
+        <v>1.087</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>2406-20-24</t>
+          <t>2406-16-06</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 7/8-12 x 1 5/8-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 9/16-18 x 1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>1 7/8-12</t>
+          <t>9/16-18</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>1 5/8-12 (female 37deg JIC)</t>
+          <t>1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
@@ -4946,29 +4946,29 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.276 from the End A tip, inside the End A thread/groove zone (0.556); radial wall there min 0.029 at 0.556 from the tip (THIN)</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>2406-20-24</t>
+          <t>2406-16-06</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2406-24-08</t>
+          <t>2406-16-08</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.09</v>
+        <v>1.72</v>
       </c>
       <c r="C34" t="n">
-        <v>1.29904</v>
+        <v>0.86603</v>
       </c>
       <c r="D34" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="E34" t="n">
         <v>0.375</v>
@@ -5013,46 +5013,46 @@
         <v>0.0625</v>
       </c>
       <c r="S34" t="n">
-        <v>0.9605</v>
+        <v>0.6585</v>
       </c>
       <c r="T34" t="n">
-        <v>0.89239</v>
+        <v>0.61114</v>
       </c>
       <c r="U34" t="n">
-        <v>0.5869</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="V34" t="n">
-        <v>1.78478</v>
+        <v>1.22228</v>
       </c>
       <c r="W34" t="n">
-        <v>0.655</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="X34" t="n">
         <v>0.08333</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.89239</v>
+        <v>0.61114</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.09</v>
+        <v>1.72</v>
       </c>
       <c r="AB34" t="n">
         <v>0.39</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.435</v>
+        <v>1.157</v>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>2406-24-08</t>
+          <t>2406-16-08</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 3/4-16 x 1 7/8-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 3/4-16 x 1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>1 7/8-12 (female 37deg JIC)</t>
+          <t>1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
@@ -5082,47 +5082,47 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.251 from the End A tip, inside the End A thread/groove zone (0.657); radial wall there min 0.023 at 0.657 from the tip (THIN)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.346 from the End A tip, inside the End A thread/groove zone (0.657); radial wall there min 0.095 at 0.657 from the tip (OK)</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>2406-24-08</t>
+          <t>2406-16-08</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2406-24-12</t>
+          <t>2406-16-10</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.19</v>
+        <v>1.79</v>
       </c>
       <c r="C35" t="n">
-        <v>1.29904</v>
+        <v>0.86603</v>
       </c>
       <c r="D35" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="E35" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="F35" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="H35" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="J35" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="K35" t="n">
         <v>60</v>
@@ -5131,64 +5131,64 @@
         <v>37</v>
       </c>
       <c r="M35" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="N35" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>0.7045</v>
+        <v>0.6213</v>
       </c>
       <c r="P35" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="R35" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="S35" t="n">
-        <v>0.9605</v>
+        <v>0.6585</v>
       </c>
       <c r="T35" t="n">
-        <v>0.89239</v>
+        <v>0.61114</v>
       </c>
       <c r="U35" t="n">
-        <v>0.5869</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="V35" t="n">
-        <v>1.78478</v>
+        <v>1.22228</v>
       </c>
       <c r="W35" t="n">
-        <v>0.655</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="X35" t="n">
         <v>0.08333</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.89239</v>
+        <v>0.61114</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.19</v>
+        <v>1.79</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.535</v>
+        <v>1.227</v>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>2406-24-12</t>
+          <t>2406-16-10</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 1/16-12 x 1 7/8-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 7/8-14 x 1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>1 1/16-12</t>
+          <t>7/8-14</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>1 7/8-12 (female 37deg JIC)</t>
+          <t>1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
@@ -5218,47 +5218,47 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.351 from the End A tip, inside the End A thread/groove zone (0.864); radial wall there min 0.085 at 0.864 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.416 from the End A tip, inside the End A thread/groove zone (0.758); radial wall there min 0.128 at 0.758 from the tip (OK)</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>2406-24-12</t>
+          <t>2406-16-10</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2406-24-16</t>
+          <t>2406-16-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.22</v>
+        <v>1.82</v>
       </c>
       <c r="C36" t="n">
-        <v>1.29904</v>
+        <v>0.86603</v>
       </c>
       <c r="D36" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="E36" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="F36" t="n">
         <v>0.125</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="K36" t="n">
         <v>60</v>
@@ -5267,13 +5267,13 @@
         <v>37</v>
       </c>
       <c r="M36" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="N36" t="n">
         <v>0.08333</v>
       </c>
       <c r="O36" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7045</v>
       </c>
       <c r="P36" t="n">
         <v>0.04511</v>
@@ -5285,46 +5285,46 @@
         <v>0.08333</v>
       </c>
       <c r="S36" t="n">
-        <v>0.9605</v>
+        <v>0.6585</v>
       </c>
       <c r="T36" t="n">
-        <v>0.89239</v>
+        <v>0.61114</v>
       </c>
       <c r="U36" t="n">
-        <v>0.5869</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="V36" t="n">
-        <v>1.78478</v>
+        <v>1.22228</v>
       </c>
       <c r="W36" t="n">
-        <v>0.655</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="X36" t="n">
         <v>0.08333</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.89239</v>
+        <v>0.61114</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.22</v>
+        <v>1.82</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.565</v>
+        <v>1.257</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>2406-24-16</t>
+          <t>2406-16-12</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 5/16-12 x 1 7/8-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 1/16-12 x 1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>1 5/16-12</t>
+          <t>1 1/16-12</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>1 7/8-12 (female 37deg JIC)</t>
+          <t>1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
@@ -5354,47 +5354,47 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.446 from the End A tip, inside the End A thread/groove zone (0.864); radial wall there min 0.157 at 0.864 from the tip (OK)</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>2406-24-16</t>
+          <t>2406-16-12</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2406-24-20</t>
+          <t>2406-16-14</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="C37" t="n">
-        <v>1.29904</v>
+        <v>0.86603</v>
       </c>
       <c r="D37" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8125</v>
+        <v>0.59375</v>
       </c>
       <c r="F37" t="n">
         <v>0.125</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4316</v>
+        <v>0.4155</v>
       </c>
       <c r="H37" t="n">
-        <v>0.753</v>
+        <v>0.534</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="J37" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="K37" t="n">
         <v>60</v>
@@ -5403,13 +5403,13 @@
         <v>37</v>
       </c>
       <c r="M37" t="n">
-        <v>1.625</v>
+        <v>1.1875</v>
       </c>
       <c r="N37" t="n">
         <v>0.08333</v>
       </c>
       <c r="O37" t="n">
-        <v>0.7986</v>
+        <v>0.7305</v>
       </c>
       <c r="P37" t="n">
         <v>0.04511</v>
@@ -5421,46 +5421,46 @@
         <v>0.08333</v>
       </c>
       <c r="S37" t="n">
-        <v>0.9605</v>
+        <v>0.6585</v>
       </c>
       <c r="T37" t="n">
-        <v>0.89239</v>
+        <v>0.61114</v>
       </c>
       <c r="U37" t="n">
-        <v>0.5869</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="V37" t="n">
-        <v>1.78478</v>
+        <v>1.22228</v>
       </c>
       <c r="W37" t="n">
-        <v>0.655</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="X37" t="n">
         <v>0.08333</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.89239</v>
+        <v>0.61114</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.08</v>
+        <v>0.72</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.485</v>
+        <v>1.297</v>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>2406-24-20</t>
+          <t>2406-16-14</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 5/8-12 x 1 7/8-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 3/16-12 x 1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -5470,12 +5470,12 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>1 5/8-12</t>
+          <t>1 3/16-12</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>1 7/8-12 (female 37deg JIC)</t>
+          <t>1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
@@ -5495,42 +5495,42 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>2406-24-20</t>
+          <t>2406-16-14</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2406-24-32</t>
+          <t>2406-16-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.14</v>
+        <v>1.71</v>
       </c>
       <c r="C38" t="n">
-        <v>1.51843</v>
+        <v>0.97572</v>
       </c>
       <c r="D38" t="n">
-        <v>2.63</v>
+        <v>1.69</v>
       </c>
       <c r="E38" t="n">
-        <v>1.25</v>
+        <v>0.8125</v>
       </c>
       <c r="F38" t="n">
         <v>0.125</v>
       </c>
       <c r="G38" t="n">
-        <v>0.7124</v>
+        <v>0.4316</v>
       </c>
       <c r="H38" t="n">
-        <v>1.19</v>
+        <v>0.753</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1292</v>
+        <v>0.1288</v>
       </c>
       <c r="J38" t="n">
-        <v>0.3318</v>
+        <v>0.2382</v>
       </c>
       <c r="K38" t="n">
         <v>60</v>
@@ -5539,13 +5539,13 @@
         <v>37</v>
       </c>
       <c r="M38" t="n">
-        <v>2.5</v>
+        <v>1.625</v>
       </c>
       <c r="N38" t="n">
         <v>0.08333</v>
       </c>
       <c r="O38" t="n">
-        <v>1.1734</v>
+        <v>0.7986</v>
       </c>
       <c r="P38" t="n">
         <v>0.04511</v>
@@ -5557,46 +5557,46 @@
         <v>0.08333</v>
       </c>
       <c r="S38" t="n">
-        <v>0.9605</v>
+        <v>0.6585</v>
       </c>
       <c r="T38" t="n">
-        <v>0.89239</v>
+        <v>0.61114</v>
       </c>
       <c r="U38" t="n">
-        <v>0.5869</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="V38" t="n">
-        <v>1.78478</v>
+        <v>1.22228</v>
       </c>
       <c r="W38" t="n">
-        <v>0.655</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="X38" t="n">
         <v>0.08333</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.89239</v>
+        <v>0.61114</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.14</v>
+        <v>1.71</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.31</v>
+        <v>0.84</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.485</v>
+        <v>1.147</v>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>2406-24-32</t>
+          <t>2406-16-20</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 2 1/2-12 x 1 7/8-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 5/8-12 x 1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -5606,12 +5606,12 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>2 1/2-12</t>
+          <t>1 5/8-12</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>1 7/8-12 (female 37deg JIC)</t>
+          <t>1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
@@ -5626,47 +5626,47 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.301 from the End A tip, inside the End A thread/groove zone (1.333); radial wall there min 0.412 at 1.333 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.336 from the End A tip, inside the End A thread/groove zone (0.958); radial wall there min 0.284 at 0.958 from the tip (OK)</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>2406-24-32</t>
+          <t>2406-16-20</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2406-32-16</t>
+          <t>2406-16-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.58</v>
+        <v>1.81</v>
       </c>
       <c r="C39" t="n">
-        <v>1.66277</v>
+        <v>1.1547</v>
       </c>
       <c r="D39" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>0.65625</v>
+        <v>0.9375</v>
       </c>
       <c r="F39" t="n">
         <v>0.125</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4365</v>
+        <v>0.5454</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5965</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1292</v>
+        <v>0.1298</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1858</v>
+        <v>0.2482</v>
       </c>
       <c r="K39" t="n">
         <v>60</v>
@@ -5675,13 +5675,13 @@
         <v>37</v>
       </c>
       <c r="M39" t="n">
-        <v>1.3125</v>
+        <v>1.875</v>
       </c>
       <c r="N39" t="n">
         <v>0.08333</v>
       </c>
       <c r="O39" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.9234</v>
       </c>
       <c r="P39" t="n">
         <v>0.04511</v>
@@ -5693,46 +5693,46 @@
         <v>0.08333</v>
       </c>
       <c r="S39" t="n">
-        <v>1.2735</v>
+        <v>0.6585</v>
       </c>
       <c r="T39" t="n">
-        <v>1.20489</v>
+        <v>0.61114</v>
       </c>
       <c r="U39" t="n">
-        <v>0.7594</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="V39" t="n">
-        <v>2.40978</v>
+        <v>1.22228</v>
       </c>
       <c r="W39" t="n">
-        <v>0.828</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="X39" t="n">
         <v>0.08333</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.20489</v>
+        <v>0.61114</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.25</v>
+        <v>0.65625</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.58</v>
+        <v>1.81</v>
       </c>
       <c r="AB39" t="n">
         <v>0.84</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.752</v>
+        <v>1.247</v>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>2406-32-16</t>
+          <t>2406-16-24</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 5/16-12 x 2 1/2-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 7/8-12 x 1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -5742,12 +5742,12 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>1 5/16-12</t>
+          <t>1 7/8-12</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>2 1/2-12 (female 37deg JIC)</t>
+          <t>1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
@@ -5762,47 +5762,47 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.153 from the End A tip, inside the End A thread/groove zone (0.911); radial wall there min 0.025 at 0.911 from the tip (THIN)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.436 from the End A tip, inside the End A thread/groove zone (1.083); radial wall there min 0.390 at 1.083 from the tip (OK)</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>2406-32-16</t>
+          <t>2406-16-24</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2406-32-20</t>
+          <t>2406-20-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.58</v>
+        <v>1.84</v>
       </c>
       <c r="C40" t="n">
-        <v>1.66277</v>
+        <v>1.1547</v>
       </c>
       <c r="D40" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8125</v>
+        <v>0.375</v>
       </c>
       <c r="F40" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4316</v>
+        <v>0.2837</v>
       </c>
       <c r="H40" t="n">
-        <v>0.753</v>
+        <v>0.3295</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1288</v>
+        <v>0.0984</v>
       </c>
       <c r="J40" t="n">
-        <v>0.2382</v>
+        <v>0.1546</v>
       </c>
       <c r="K40" t="n">
         <v>60</v>
@@ -5811,64 +5811,64 @@
         <v>37</v>
       </c>
       <c r="M40" t="n">
-        <v>1.625</v>
+        <v>0.75</v>
       </c>
       <c r="N40" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="O40" t="n">
-        <v>0.7986</v>
+        <v>0.5367</v>
       </c>
       <c r="P40" t="n">
-        <v>0.04511</v>
+        <v>0.03383</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.02083</v>
+        <v>0.01562</v>
       </c>
       <c r="R40" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="S40" t="n">
-        <v>1.2735</v>
+        <v>0.835</v>
       </c>
       <c r="T40" t="n">
-        <v>1.20489</v>
+        <v>0.76739</v>
       </c>
       <c r="U40" t="n">
-        <v>0.7594</v>
+        <v>0.4954</v>
       </c>
       <c r="V40" t="n">
-        <v>2.40978</v>
+        <v>1.53478</v>
       </c>
       <c r="W40" t="n">
-        <v>0.828</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="X40" t="n">
         <v>0.08333</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.20489</v>
+        <v>0.76739</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.25</v>
+        <v>0.8125</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.58</v>
+        <v>1.84</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.08</v>
+        <v>0.39</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.752</v>
+        <v>1.277</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>2406-32-20</t>
+          <t>2406-20-08</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 5/8-12 x 2 1/2-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 3/4-16 x 1 5/8-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>1 5/8-12</t>
+          <t>3/4-16</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>2 1/2-12 (female 37deg JIC)</t>
+          <t>1 5/8-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
@@ -5898,47 +5898,47 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.153 from the End A tip, inside the End A thread/groove zone (0.958); radial wall there min 0.146 at 0.958 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.259 from the End A tip, inside the End A thread/groove zone (0.657); radial wall there min 0.029 at 0.657 from the tip (THIN)</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>2406-32-20</t>
+          <t>2406-20-08</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2406-32-24</t>
+          <t>2406-20-10</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.61</v>
+        <v>1.91</v>
       </c>
       <c r="C41" t="n">
-        <v>1.66277</v>
+        <v>1.1547</v>
       </c>
       <c r="D41" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9375</v>
+        <v>0.4375</v>
       </c>
       <c r="F41" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="G41" t="n">
-        <v>0.5454</v>
+        <v>0.3553</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.386</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1298</v>
+        <v>0.1114</v>
       </c>
       <c r="J41" t="n">
-        <v>0.2482</v>
+        <v>0.1546</v>
       </c>
       <c r="K41" t="n">
         <v>60</v>
@@ -5947,97 +5947,1593 @@
         <v>37</v>
       </c>
       <c r="M41" t="n">
-        <v>1.875</v>
+        <v>0.875</v>
       </c>
       <c r="N41" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="O41" t="n">
-        <v>0.9234</v>
+        <v>0.6213</v>
       </c>
       <c r="P41" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="R41" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="S41" t="n">
-        <v>1.2735</v>
+        <v>0.835</v>
       </c>
       <c r="T41" t="n">
-        <v>1.20489</v>
+        <v>0.76739</v>
       </c>
       <c r="U41" t="n">
-        <v>0.7594</v>
+        <v>0.4954</v>
       </c>
       <c r="V41" t="n">
-        <v>2.40978</v>
+        <v>1.53478</v>
       </c>
       <c r="W41" t="n">
-        <v>0.828</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="X41" t="n">
         <v>0.08333</v>
       </c>
       <c r="Y41" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.347</v>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>2406-20-10</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>Female JIC x Male JIC Reducer/Expander, 7/8-14 x 1 5/8-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>7/8-14</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.329 from the End A tip, inside the End A thread/groove zone (0.758); radial wall there min 0.062 at 0.758 from the tip (OK)</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>2406-20-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2406-20-12</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.1547</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="K42" t="n">
+        <v>60</v>
+      </c>
+      <c r="L42" t="n">
+        <v>37</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.7045</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.4954</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.53478</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.457</v>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>2406-20-12</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 1/16-12 x 1 5/8-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>1 1/16-12</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology. | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p007-t03: agrees on HEXB@HEX, D3@BORE; DIFFERS on L23@DRIVE 2.02 vs Brennan L0 LGTH 2.000 (built to the dimension source, s6)) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.439 from the End A tip, inside the End A thread/groove zone (0.864); radial wall there min 0.151 at 0.864 from the tip (OK)</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>2406-20-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2406-20-16</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.1547</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="K43" t="n">
+        <v>60</v>
+      </c>
+      <c r="L43" t="n">
+        <v>37</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.7514999999999999</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0.4954</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.53478</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.447</v>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>2406-20-16</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 5/16-12 x 1 5/8-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>1 5/16-12</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology. | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p008-t01: agrees on HEXB@HEX, D3@BORE; DIFFERS on L23@DRIVE 2.01 vs Brennan L0 LGTH 2.000 (built to the dimension source, s6)) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>2406-20-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2406-20-24</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1.1547</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="K44" t="n">
+        <v>60</v>
+      </c>
+      <c r="L44" t="n">
+        <v>37</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.9234</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0.4954</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.53478</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.577</v>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>2406-20-24</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 7/8-12 x 1 5/8-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>1 7/8-12</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>2406-20-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2406-24-08</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1.29904</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="K45" t="n">
+        <v>60</v>
+      </c>
+      <c r="L45" t="n">
+        <v>37</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.5367</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.9605</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0.5869</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.78478</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.435</v>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>2406-24-08</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>Female JIC x Male JIC Reducer/Expander, 3/4-16 x 1 7/8-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>3/4-16</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.251 from the End A tip, inside the End A thread/groove zone (0.657); radial wall there min 0.023 at 0.657 from the tip (THIN)</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>2406-24-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2406-24-12</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1.29904</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="K46" t="n">
+        <v>60</v>
+      </c>
+      <c r="L46" t="n">
+        <v>37</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.7045</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.9605</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0.5869</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.78478</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.535</v>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>2406-24-12</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 1/16-12 x 1 7/8-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>1 1/16-12</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.351 from the End A tip, inside the End A thread/groove zone (0.864); radial wall there min 0.085 at 0.864 from the tip (OK)</t>
+        </is>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>2406-24-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2406-24-16</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1.29904</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="K47" t="n">
+        <v>60</v>
+      </c>
+      <c r="L47" t="n">
+        <v>37</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.7514999999999999</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.9605</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0.5869</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.78478</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.565</v>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>2406-24-16</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 5/16-12 x 1 7/8-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>1 5/16-12</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>2406-24-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2406-24-20</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1.29904</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="K48" t="n">
+        <v>60</v>
+      </c>
+      <c r="L48" t="n">
+        <v>37</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.7986</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.9605</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0.5869</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.78478</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.485</v>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>2406-24-20</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 5/8-12 x 1 7/8-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>1 5/8-12</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>2406-24-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2406-24-32</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1.51843</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="K49" t="n">
+        <v>60</v>
+      </c>
+      <c r="L49" t="n">
+        <v>37</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1.1734</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.9605</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0.5869</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.78478</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.485</v>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>2406-24-32</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>Female JIC x Male JIC Reducer/Expander, 2 1/2-12 x 1 7/8-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>2 1/2-12</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.301 from the End A tip, inside the End A thread/groove zone (1.333); radial wall there min 0.412 at 1.333 from the tip (OK)</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>2406-24-32</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2406-32-16</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1.66277</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="K50" t="n">
+        <v>60</v>
+      </c>
+      <c r="L50" t="n">
+        <v>37</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.7514999999999999</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1.2735</v>
+      </c>
+      <c r="T50" t="n">
         <v>1.20489</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="U50" t="n">
+        <v>0.7594</v>
+      </c>
+      <c r="V50" t="n">
+        <v>2.40978</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="Z50" t="n">
         <v>1.25</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AA50" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.752</v>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>2406-32-16</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 5/16-12 x 2 1/2-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>1 5/16-12</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.153 from the End A tip, inside the End A thread/groove zone (0.911); radial wall there min 0.025 at 0.911 from the tip (THIN)</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>2406-32-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2406-32-20</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1.66277</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="K51" t="n">
+        <v>60</v>
+      </c>
+      <c r="L51" t="n">
+        <v>37</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.7986</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1.2735</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0.7594</v>
+      </c>
+      <c r="V51" t="n">
+        <v>2.40978</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.752</v>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>2406-32-20</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 5/8-12 x 2 1/2-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>1 5/8-12</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.153 from the End A tip, inside the End A thread/groove zone (0.958); radial wall there min 0.146 at 0.958 from the tip (OK)</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>2406-32-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2406-32-24</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
         <v>2.61</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="C52" t="n">
+        <v>1.66277</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="K52" t="n">
+        <v>60</v>
+      </c>
+      <c r="L52" t="n">
+        <v>37</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.9234</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1.2735</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0.7594</v>
+      </c>
+      <c r="V52" t="n">
+        <v>2.40978</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AB52" t="n">
         <v>1.31</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AC52" t="n">
         <v>1.782</v>
       </c>
-      <c r="AD41" t="inlineStr">
+      <c r="AD52" t="inlineStr">
         <is>
           <t>2406-32-24</t>
         </is>
       </c>
-      <c r="AE41" t="inlineStr">
+      <c r="AE52" t="inlineStr">
         <is>
           <t>Female JIC x Male JIC Reducer/Expander, 1 7/8-12 x 2 1/2-12 (female 37deg JIC)</t>
         </is>
       </c>
-      <c r="AF41" t="inlineStr">
+      <c r="AF52" t="inlineStr">
         <is>
           <t>2406</t>
         </is>
       </c>
-      <c r="AG41" t="inlineStr">
+      <c r="AG52" t="inlineStr">
         <is>
           <t>1 7/8-12</t>
         </is>
       </c>
-      <c r="AH41" t="inlineStr">
+      <c r="AH52" t="inlineStr">
         <is>
           <t>2 1/2-12 (female 37deg JIC)</t>
         </is>
       </c>
-      <c r="AI41" t="inlineStr">
+      <c r="AI52" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AJ41" t="inlineStr">
+      <c r="AJ52" t="inlineStr">
         <is>
           <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
         </is>
       </c>
-      <c r="AK41" t="inlineStr">
+      <c r="AK52" t="inlineStr">
         <is>
           <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.183 from the End A tip, inside the End A thread/groove zone (1.083); radial wall there min 0.199 at 1.083 from the tip (OK)</t>
         </is>
       </c>
-      <c r="AL41" t="inlineStr">
+      <c r="AL52" t="inlineStr">
         <is>
           <t>2406-32-24</t>
         </is>

--- a/04_DESIGN_TABLES/DesignTable_2406_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2406_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL52"/>
+  <dimension ref="A1:AL53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4822,11 +4822,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2406-16-06</t>
+          <t>2406-16-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="C33" t="n">
         <v>0.86603</v>
@@ -4835,22 +4835,22 @@
         <v>1.5</v>
       </c>
       <c r="E33" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="F33" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="K33" t="n">
         <v>60</v>
@@ -4859,22 +4859,22 @@
         <v>37</v>
       </c>
       <c r="M33" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="N33" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="O33" t="n">
-        <v>0.4495</v>
+        <v>0.4538</v>
       </c>
       <c r="P33" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="R33" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="S33" t="n">
         <v>0.6585</v>
@@ -4901,22 +4901,22 @@
         <v>0.65625</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.087</v>
+        <v>1.277</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>2406-16-06</t>
+          <t>2406-16-04</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 9/16-18 x 1 5/16-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 7/16-20 x 1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>9/16-18</t>
+          <t>7/16-20</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
@@ -4941,28 +4941,28 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+          <t>[BRENNAN-CELL 2026-10-20: L23@DRIVE] Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source); L23@DRIVE: Brennan TFA catalog p.7 table TFA-p007-t03 "FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)" row 2406-16-04 col "L0 LGTH" = 1.840 (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_index.json, page verified True) [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan ("use brennans")] (Air-Way printed 1.67: with L23 1.67 the -16 female JIC port (seat measured on the Brennan 2406 STEPs, JICF_MEAS[16]) reaches the -04 male end: radial wall -0.009 at 0.550 from the male tip (generator BLOCKED "wall between the female port and the End A thread root/groove"); same dimension (overall length): L23 = Brennan L0 to rounding on 25 of the 56 2406 rows Brennan prints, Air-Way shorter on most others (2406-16-06 1.65 vs 1.84)) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.276 from the End A tip, inside the End A thread/groove zone (0.556); radial wall there min 0.029 at 0.556 from the tip (THIN)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology. | 2026-10-20 L23@DRIVE = Brennan 1.84 (Air-Way 1.67 cannot be built: with L23 1.67 the -16 female JIC port (seat measured on the Brennan 2406 STEPs, JICF_MEAS[16]) reaches the -04 male end: radial wall -0.009 at 0.550 from the male tip (generator BLOCKED "wall between the female port and the End A thread root/groove"); same dimension (overall length): L23 = Brennan L0 to rounding on 25 of the 56 2406 rows Brennan prints, Air-Way shorter on most others (2406-16-06 1.65 vs 1.84))) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>2406-16-06</t>
+          <t>2406-16-04</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2406-16-08</t>
+          <t>2406-16-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="C34" t="n">
         <v>0.86603</v>
@@ -4971,22 +4971,22 @@
         <v>1.5</v>
       </c>
       <c r="E34" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="F34" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2837</v>
+        <v>0.2515</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3295</v>
+        <v>0.2405</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0984</v>
+        <v>0.0898</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="K34" t="n">
         <v>60</v>
@@ -4995,22 +4995,22 @@
         <v>37</v>
       </c>
       <c r="M34" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="N34" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="O34" t="n">
-        <v>0.5367</v>
+        <v>0.4495</v>
       </c>
       <c r="P34" t="n">
-        <v>0.03383</v>
+        <v>0.03007</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.01562</v>
+        <v>0.01389</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="S34" t="n">
         <v>0.6585</v>
@@ -5037,22 +5037,22 @@
         <v>0.65625</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.157</v>
+        <v>1.087</v>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>2406-16-08</t>
+          <t>2406-16-06</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 3/4-16 x 1 5/16-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 9/16-18 x 1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>3/4-16</t>
+          <t>9/16-18</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
@@ -5082,23 +5082,23 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.346 from the End A tip, inside the End A thread/groove zone (0.657); radial wall there min 0.095 at 0.657 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.276 from the End A tip, inside the End A thread/groove zone (0.556); radial wall there min 0.029 at 0.556 from the tip (THIN)</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>2406-16-08</t>
+          <t>2406-16-06</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2406-16-10</t>
+          <t>2406-16-08</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="C35" t="n">
         <v>0.86603</v>
@@ -5107,19 +5107,19 @@
         <v>1.5</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="F35" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3553</v>
+        <v>0.2837</v>
       </c>
       <c r="H35" t="n">
-        <v>0.386</v>
+        <v>0.3295</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1114</v>
+        <v>0.0984</v>
       </c>
       <c r="J35" t="n">
         <v>0.1546</v>
@@ -5131,22 +5131,22 @@
         <v>37</v>
       </c>
       <c r="M35" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="N35" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="O35" t="n">
-        <v>0.6213</v>
+        <v>0.5367</v>
       </c>
       <c r="P35" t="n">
-        <v>0.03866</v>
+        <v>0.03383</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.01786</v>
+        <v>0.01562</v>
       </c>
       <c r="R35" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="S35" t="n">
         <v>0.6585</v>
@@ -5173,22 +5173,22 @@
         <v>0.65625</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.48</v>
+        <v>0.39</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.227</v>
+        <v>1.157</v>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>2406-16-10</t>
+          <t>2406-16-08</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 7/8-14 x 1 5/16-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 3/4-16 x 1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>7/8-14</t>
+          <t>3/4-16</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
@@ -5218,23 +5218,23 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.416 from the End A tip, inside the End A thread/groove zone (0.758); radial wall there min 0.128 at 0.758 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.346 from the End A tip, inside the End A thread/groove zone (0.657); radial wall there min 0.095 at 0.657 from the tip (OK)</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>2406-16-10</t>
+          <t>2406-16-08</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2406-16-12</t>
+          <t>2406-16-10</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="C36" t="n">
         <v>0.86603</v>
@@ -5243,22 +5243,22 @@
         <v>1.5</v>
       </c>
       <c r="E36" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="F36" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="K36" t="n">
         <v>60</v>
@@ -5267,22 +5267,22 @@
         <v>37</v>
       </c>
       <c r="M36" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="N36" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="O36" t="n">
-        <v>0.7045</v>
+        <v>0.6213</v>
       </c>
       <c r="P36" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="R36" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="S36" t="n">
         <v>0.6585</v>
@@ -5309,22 +5309,22 @@
         <v>0.65625</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.257</v>
+        <v>1.227</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>2406-16-12</t>
+          <t>2406-16-10</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 1/16-12 x 1 5/16-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 7/8-14 x 1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>1 1/16-12</t>
+          <t>7/8-14</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
@@ -5354,23 +5354,23 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.446 from the End A tip, inside the End A thread/groove zone (0.864); radial wall there min 0.157 at 0.864 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.416 from the End A tip, inside the End A thread/groove zone (0.758); radial wall there min 0.128 at 0.758 from the tip (OK)</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>2406-16-12</t>
+          <t>2406-16-10</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2406-16-14</t>
+          <t>2406-16-12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="C37" t="n">
         <v>0.86603</v>
@@ -5379,22 +5379,22 @@
         <v>1.5</v>
       </c>
       <c r="E37" t="n">
-        <v>0.59375</v>
+        <v>0.53125</v>
       </c>
       <c r="F37" t="n">
         <v>0.125</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4155</v>
+        <v>0.3895</v>
       </c>
       <c r="H37" t="n">
-        <v>0.534</v>
+        <v>0.4715</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="J37" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="K37" t="n">
         <v>60</v>
@@ -5403,13 +5403,13 @@
         <v>37</v>
       </c>
       <c r="M37" t="n">
-        <v>1.1875</v>
+        <v>1.0625</v>
       </c>
       <c r="N37" t="n">
         <v>0.08333</v>
       </c>
       <c r="O37" t="n">
-        <v>0.7305</v>
+        <v>0.7045</v>
       </c>
       <c r="P37" t="n">
         <v>0.04511</v>
@@ -5445,22 +5445,22 @@
         <v>0.65625</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.297</v>
+        <v>1.257</v>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>2406-16-14</t>
+          <t>2406-16-12</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 3/16-12 x 1 5/16-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 1/16-12 x 1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>1 3/16-12</t>
+          <t>1 1/16-12</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
@@ -5490,47 +5490,47 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.446 from the End A tip, inside the End A thread/groove zone (0.864); radial wall there min 0.157 at 0.864 from the tip (OK)</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>2406-16-14</t>
+          <t>2406-16-12</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2406-16-20</t>
+          <t>2406-16-14</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="C38" t="n">
-        <v>0.97572</v>
+        <v>0.86603</v>
       </c>
       <c r="D38" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8125</v>
+        <v>0.59375</v>
       </c>
       <c r="F38" t="n">
         <v>0.125</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4316</v>
+        <v>0.4155</v>
       </c>
       <c r="H38" t="n">
-        <v>0.753</v>
+        <v>0.534</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="J38" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="K38" t="n">
         <v>60</v>
@@ -5539,13 +5539,13 @@
         <v>37</v>
       </c>
       <c r="M38" t="n">
-        <v>1.625</v>
+        <v>1.1875</v>
       </c>
       <c r="N38" t="n">
         <v>0.08333</v>
       </c>
       <c r="O38" t="n">
-        <v>0.7986</v>
+        <v>0.7305</v>
       </c>
       <c r="P38" t="n">
         <v>0.04511</v>
@@ -5581,22 +5581,22 @@
         <v>0.65625</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.147</v>
+        <v>1.297</v>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>2406-16-20</t>
+          <t>2406-16-14</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 5/8-12 x 1 5/16-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 3/16-12 x 1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>1 5/8-12</t>
+          <t>1 3/16-12</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
@@ -5626,47 +5626,47 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.336 from the End A tip, inside the End A thread/groove zone (0.958); radial wall there min 0.284 at 0.958 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>2406-16-20</t>
+          <t>2406-16-14</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2406-16-24</t>
+          <t>2406-16-20</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="C39" t="n">
-        <v>1.1547</v>
+        <v>0.97572</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="F39" t="n">
         <v>0.125</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1298</v>
+        <v>0.1288</v>
       </c>
       <c r="J39" t="n">
-        <v>0.2482</v>
+        <v>0.2382</v>
       </c>
       <c r="K39" t="n">
         <v>60</v>
@@ -5675,13 +5675,13 @@
         <v>37</v>
       </c>
       <c r="M39" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="N39" t="n">
         <v>0.08333</v>
       </c>
       <c r="O39" t="n">
-        <v>0.9234</v>
+        <v>0.7986</v>
       </c>
       <c r="P39" t="n">
         <v>0.04511</v>
@@ -5717,22 +5717,22 @@
         <v>0.65625</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AB39" t="n">
         <v>0.84</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.247</v>
+        <v>1.147</v>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>2406-16-24</t>
+          <t>2406-16-20</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 7/8-12 x 1 5/16-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 5/8-12 x 1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>1 7/8-12</t>
+          <t>1 5/8-12</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
@@ -5762,23 +5762,23 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.436 from the End A tip, inside the End A thread/groove zone (1.083); radial wall there min 0.390 at 1.083 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.336 from the End A tip, inside the End A thread/groove zone (0.958); radial wall there min 0.284 at 0.958 from the tip (OK)</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>2406-16-24</t>
+          <t>2406-16-20</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2406-20-08</t>
+          <t>2406-16-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="C40" t="n">
         <v>1.1547</v>
@@ -5787,22 +5787,22 @@
         <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>0.375</v>
+        <v>0.9375</v>
       </c>
       <c r="F40" t="n">
-        <v>0.094</v>
+        <v>0.125</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2837</v>
+        <v>0.5454</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3295</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0984</v>
+        <v>0.1298</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1546</v>
+        <v>0.2482</v>
       </c>
       <c r="K40" t="n">
         <v>60</v>
@@ -5811,34 +5811,34 @@
         <v>37</v>
       </c>
       <c r="M40" t="n">
-        <v>0.75</v>
+        <v>1.875</v>
       </c>
       <c r="N40" t="n">
-        <v>0.0625</v>
+        <v>0.08333</v>
       </c>
       <c r="O40" t="n">
-        <v>0.5367</v>
+        <v>0.9234</v>
       </c>
       <c r="P40" t="n">
-        <v>0.03383</v>
+        <v>0.04511</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.01562</v>
+        <v>0.02083</v>
       </c>
       <c r="R40" t="n">
-        <v>0.0625</v>
+        <v>0.08333</v>
       </c>
       <c r="S40" t="n">
-        <v>0.835</v>
+        <v>0.6585</v>
       </c>
       <c r="T40" t="n">
-        <v>0.76739</v>
+        <v>0.61114</v>
       </c>
       <c r="U40" t="n">
-        <v>0.4954</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="V40" t="n">
-        <v>1.53478</v>
+        <v>1.22228</v>
       </c>
       <c r="W40" t="n">
         <v>0.5629999999999999</v>
@@ -5847,28 +5847,28 @@
         <v>0.08333</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.76739</v>
+        <v>0.61114</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.39</v>
+        <v>0.84</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.277</v>
+        <v>1.247</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>2406-20-08</t>
+          <t>2406-16-24</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 3/4-16 x 1 5/8-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 7/8-12 x 1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>3/4-16</t>
+          <t>1 7/8-12</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>1 5/8-12 (female 37deg JIC)</t>
+          <t>1 5/16-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
@@ -5898,23 +5898,23 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.259 from the End A tip, inside the End A thread/groove zone (0.657); radial wall there min 0.029 at 0.657 from the tip (THIN)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.436 from the End A tip, inside the End A thread/groove zone (1.083); radial wall there min 0.390 at 1.083 from the tip (OK)</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>2406-20-08</t>
+          <t>2406-16-24</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2406-20-10</t>
+          <t>2406-20-08</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="C41" t="n">
         <v>1.1547</v>
@@ -5923,19 +5923,19 @@
         <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="F41" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3553</v>
+        <v>0.2837</v>
       </c>
       <c r="H41" t="n">
-        <v>0.386</v>
+        <v>0.3295</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1114</v>
+        <v>0.0984</v>
       </c>
       <c r="J41" t="n">
         <v>0.1546</v>
@@ -5947,22 +5947,22 @@
         <v>37</v>
       </c>
       <c r="M41" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="N41" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="O41" t="n">
-        <v>0.6213</v>
+        <v>0.5367</v>
       </c>
       <c r="P41" t="n">
-        <v>0.03866</v>
+        <v>0.03383</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.01786</v>
+        <v>0.01562</v>
       </c>
       <c r="R41" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="S41" t="n">
         <v>0.835</v>
@@ -5989,22 +5989,22 @@
         <v>0.8125</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.48</v>
+        <v>0.39</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.347</v>
+        <v>1.277</v>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>2406-20-10</t>
+          <t>2406-20-08</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 7/8-14 x 1 5/8-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 3/4-16 x 1 5/8-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>7/8-14</t>
+          <t>3/4-16</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
@@ -6034,23 +6034,23 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.329 from the End A tip, inside the End A thread/groove zone (0.758); radial wall there min 0.062 at 0.758 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.259 from the End A tip, inside the End A thread/groove zone (0.657); radial wall there min 0.029 at 0.657 from the tip (THIN)</t>
         </is>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>2406-20-10</t>
+          <t>2406-20-08</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2406-20-12</t>
+          <t>2406-20-10</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="C42" t="n">
         <v>1.1547</v>
@@ -6059,22 +6059,22 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="F42" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="G42" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="J42" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="K42" t="n">
         <v>60</v>
@@ -6083,22 +6083,22 @@
         <v>37</v>
       </c>
       <c r="M42" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="N42" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="O42" t="n">
-        <v>0.7045</v>
+        <v>0.6213</v>
       </c>
       <c r="P42" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="R42" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="S42" t="n">
         <v>0.835</v>
@@ -6125,22 +6125,22 @@
         <v>0.8125</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.457</v>
+        <v>1.347</v>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>2406-20-12</t>
+          <t>2406-20-10</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 1/16-12 x 1 5/8-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 7/8-14 x 1 5/8-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>1 1/16-12</t>
+          <t>7/8-14</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
@@ -6170,23 +6170,23 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology. | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p007-t03: agrees on HEXB@HEX, D3@BORE; DIFFERS on L23@DRIVE 2.02 vs Brennan L0 LGTH 2.000 (built to the dimension source, s6)) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.439 from the End A tip, inside the End A thread/groove zone (0.864); radial wall there min 0.151 at 0.864 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.329 from the End A tip, inside the End A thread/groove zone (0.758); radial wall there min 0.062 at 0.758 from the tip (OK)</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>2406-20-12</t>
+          <t>2406-20-10</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2406-20-16</t>
+          <t>2406-20-12</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="C43" t="n">
         <v>1.1547</v>
@@ -6195,22 +6195,22 @@
         <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="F43" t="n">
         <v>0.125</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="J43" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="K43" t="n">
         <v>60</v>
@@ -6219,13 +6219,13 @@
         <v>37</v>
       </c>
       <c r="M43" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="N43" t="n">
         <v>0.08333</v>
       </c>
       <c r="O43" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7045</v>
       </c>
       <c r="P43" t="n">
         <v>0.04511</v>
@@ -6261,22 +6261,22 @@
         <v>0.8125</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.447</v>
+        <v>1.457</v>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>2406-20-16</t>
+          <t>2406-20-12</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 5/16-12 x 1 5/8-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 1/16-12 x 1 5/8-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>1 5/16-12</t>
+          <t>1 1/16-12</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
@@ -6306,23 +6306,23 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology. | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p008-t01: agrees on HEXB@HEX, D3@BORE; DIFFERS on L23@DRIVE 2.01 vs Brennan L0 LGTH 2.000 (built to the dimension source, s6)) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology. | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p007-t03: agrees on HEXB@HEX, D3@BORE; DIFFERS on L23@DRIVE 2.02 vs Brennan L0 LGTH 2.000 (built to the dimension source, s6)) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.439 from the End A tip, inside the End A thread/groove zone (0.864); radial wall there min 0.151 at 0.864 from the tip (OK)</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>2406-20-16</t>
+          <t>2406-20-12</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2406-20-24</t>
+          <t>2406-20-16</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="C44" t="n">
         <v>1.1547</v>
@@ -6331,22 +6331,22 @@
         <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="F44" t="n">
         <v>0.125</v>
       </c>
       <c r="G44" t="n">
-        <v>0.5454</v>
+        <v>0.4365</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.5965</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1298</v>
+        <v>0.1292</v>
       </c>
       <c r="J44" t="n">
-        <v>0.2482</v>
+        <v>0.1858</v>
       </c>
       <c r="K44" t="n">
         <v>60</v>
@@ -6355,13 +6355,13 @@
         <v>37</v>
       </c>
       <c r="M44" t="n">
-        <v>1.875</v>
+        <v>1.3125</v>
       </c>
       <c r="N44" t="n">
         <v>0.08333</v>
       </c>
       <c r="O44" t="n">
-        <v>0.9234</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="P44" t="n">
         <v>0.04511</v>
@@ -6397,22 +6397,22 @@
         <v>0.8125</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.577</v>
+        <v>1.447</v>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>2406-20-24</t>
+          <t>2406-20-16</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 7/8-12 x 1 5/8-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 5/16-12 x 1 5/8-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>1 7/8-12</t>
+          <t>1 5/16-12</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
@@ -6442,47 +6442,47 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology. | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p008-t01: agrees on HEXB@HEX, D3@BORE; DIFFERS on L23@DRIVE 2.01 vs Brennan L0 LGTH 2.000 (built to the dimension source, s6)) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>2406-20-24</t>
+          <t>2406-20-16</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2406-24-08</t>
+          <t>2406-20-24</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="C45" t="n">
-        <v>1.29904</v>
+        <v>1.1547</v>
       </c>
       <c r="D45" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>0.375</v>
+        <v>0.9375</v>
       </c>
       <c r="F45" t="n">
-        <v>0.094</v>
+        <v>0.125</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2837</v>
+        <v>0.5454</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3295</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0984</v>
+        <v>0.1298</v>
       </c>
       <c r="J45" t="n">
-        <v>0.1546</v>
+        <v>0.2482</v>
       </c>
       <c r="K45" t="n">
         <v>60</v>
@@ -6491,64 +6491,64 @@
         <v>37</v>
       </c>
       <c r="M45" t="n">
-        <v>0.75</v>
+        <v>1.875</v>
       </c>
       <c r="N45" t="n">
-        <v>0.0625</v>
+        <v>0.08333</v>
       </c>
       <c r="O45" t="n">
-        <v>0.5367</v>
+        <v>0.9234</v>
       </c>
       <c r="P45" t="n">
-        <v>0.03383</v>
+        <v>0.04511</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.01562</v>
+        <v>0.02083</v>
       </c>
       <c r="R45" t="n">
-        <v>0.0625</v>
+        <v>0.08333</v>
       </c>
       <c r="S45" t="n">
-        <v>0.9605</v>
+        <v>0.835</v>
       </c>
       <c r="T45" t="n">
-        <v>0.89239</v>
+        <v>0.76739</v>
       </c>
       <c r="U45" t="n">
-        <v>0.5869</v>
+        <v>0.4954</v>
       </c>
       <c r="V45" t="n">
-        <v>1.78478</v>
+        <v>1.53478</v>
       </c>
       <c r="W45" t="n">
-        <v>0.655</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="X45" t="n">
         <v>0.08333</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.89239</v>
+        <v>0.76739</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.39</v>
+        <v>1.08</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.435</v>
+        <v>1.577</v>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>2406-24-08</t>
+          <t>2406-20-24</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 3/4-16 x 1 7/8-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 7/8-12 x 1 5/8-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -6558,12 +6558,12 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>3/4-16</t>
+          <t>1 7/8-12</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>1 7/8-12 (female 37deg JIC)</t>
+          <t>1 5/8-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
@@ -6578,23 +6578,23 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.251 from the End A tip, inside the End A thread/groove zone (0.657); radial wall there min 0.023 at 0.657 from the tip (THIN)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>2406-24-08</t>
+          <t>2406-20-24</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2406-24-12</t>
+          <t>2406-24-08</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="C46" t="n">
         <v>1.29904</v>
@@ -6603,22 +6603,22 @@
         <v>2.25</v>
       </c>
       <c r="E46" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="F46" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3895</v>
+        <v>0.2837</v>
       </c>
       <c r="H46" t="n">
-        <v>0.4715</v>
+        <v>0.3295</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1299</v>
+        <v>0.0984</v>
       </c>
       <c r="J46" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="K46" t="n">
         <v>60</v>
@@ -6627,22 +6627,22 @@
         <v>37</v>
       </c>
       <c r="M46" t="n">
-        <v>1.0625</v>
+        <v>0.75</v>
       </c>
       <c r="N46" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="O46" t="n">
-        <v>0.7045</v>
+        <v>0.5367</v>
       </c>
       <c r="P46" t="n">
-        <v>0.04511</v>
+        <v>0.03383</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.02083</v>
+        <v>0.01562</v>
       </c>
       <c r="R46" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="S46" t="n">
         <v>0.9605</v>
@@ -6669,22 +6669,22 @@
         <v>0.9375</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.61</v>
+        <v>0.39</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.535</v>
+        <v>1.435</v>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>2406-24-12</t>
+          <t>2406-24-08</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 1/16-12 x 1 7/8-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 3/4-16 x 1 7/8-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>1 1/16-12</t>
+          <t>3/4-16</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr">
@@ -6714,23 +6714,23 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.351 from the End A tip, inside the End A thread/groove zone (0.864); radial wall there min 0.085 at 0.864 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.251 from the End A tip, inside the End A thread/groove zone (0.657); radial wall there min 0.023 at 0.657 from the tip (THIN)</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>2406-24-12</t>
+          <t>2406-24-08</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2406-24-16</t>
+          <t>2406-24-12</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="C47" t="n">
         <v>1.29904</v>
@@ -6739,22 +6739,22 @@
         <v>2.25</v>
       </c>
       <c r="E47" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="F47" t="n">
         <v>0.125</v>
       </c>
       <c r="G47" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="H47" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="J47" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="K47" t="n">
         <v>60</v>
@@ -6763,13 +6763,13 @@
         <v>37</v>
       </c>
       <c r="M47" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="N47" t="n">
         <v>0.08333</v>
       </c>
       <c r="O47" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7045</v>
       </c>
       <c r="P47" t="n">
         <v>0.04511</v>
@@ -6805,22 +6805,22 @@
         <v>0.9375</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.565</v>
+        <v>1.535</v>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>2406-24-16</t>
+          <t>2406-24-12</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 5/16-12 x 1 7/8-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 1/16-12 x 1 7/8-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>1 5/16-12</t>
+          <t>1 1/16-12</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
@@ -6850,23 +6850,23 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.351 from the End A tip, inside the End A thread/groove zone (0.864); radial wall there min 0.085 at 0.864 from the tip (OK)</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>2406-24-16</t>
+          <t>2406-24-12</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2406-24-20</t>
+          <t>2406-24-16</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="C48" t="n">
         <v>1.29904</v>
@@ -6875,22 +6875,22 @@
         <v>2.25</v>
       </c>
       <c r="E48" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="F48" t="n">
         <v>0.125</v>
       </c>
       <c r="G48" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="H48" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="J48" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="K48" t="n">
         <v>60</v>
@@ -6899,13 +6899,13 @@
         <v>37</v>
       </c>
       <c r="M48" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="N48" t="n">
         <v>0.08333</v>
       </c>
       <c r="O48" t="n">
-        <v>0.7986</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="P48" t="n">
         <v>0.04511</v>
@@ -6941,22 +6941,22 @@
         <v>0.9375</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.485</v>
+        <v>1.565</v>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>2406-24-20</t>
+          <t>2406-24-16</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 5/8-12 x 1 7/8-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 5/16-12 x 1 7/8-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>1 5/8-12</t>
+          <t>1 5/16-12</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
@@ -6991,42 +6991,42 @@
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>2406-24-20</t>
+          <t>2406-24-16</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2406-24-32</t>
+          <t>2406-24-20</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>2.14</v>
       </c>
       <c r="C49" t="n">
-        <v>1.51843</v>
+        <v>1.29904</v>
       </c>
       <c r="D49" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="E49" t="n">
-        <v>1.25</v>
+        <v>0.8125</v>
       </c>
       <c r="F49" t="n">
         <v>0.125</v>
       </c>
       <c r="G49" t="n">
-        <v>0.7124</v>
+        <v>0.4316</v>
       </c>
       <c r="H49" t="n">
-        <v>1.19</v>
+        <v>0.753</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1292</v>
+        <v>0.1288</v>
       </c>
       <c r="J49" t="n">
-        <v>0.3318</v>
+        <v>0.2382</v>
       </c>
       <c r="K49" t="n">
         <v>60</v>
@@ -7035,13 +7035,13 @@
         <v>37</v>
       </c>
       <c r="M49" t="n">
-        <v>2.5</v>
+        <v>1.625</v>
       </c>
       <c r="N49" t="n">
         <v>0.08333</v>
       </c>
       <c r="O49" t="n">
-        <v>1.1734</v>
+        <v>0.7986</v>
       </c>
       <c r="P49" t="n">
         <v>0.04511</v>
@@ -7080,19 +7080,19 @@
         <v>2.14</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AC49" t="n">
         <v>1.485</v>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>2406-24-32</t>
+          <t>2406-24-20</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 2 1/2-12 x 1 7/8-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 5/8-12 x 1 7/8-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>2 1/2-12</t>
+          <t>1 5/8-12</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
@@ -7122,47 +7122,47 @@
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.301 from the End A tip, inside the End A thread/groove zone (1.333); radial wall there min 0.412 at 1.333 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>2406-24-32</t>
+          <t>2406-24-20</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2406-32-16</t>
+          <t>2406-24-32</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.58</v>
+        <v>2.14</v>
       </c>
       <c r="C50" t="n">
-        <v>1.66277</v>
+        <v>1.51843</v>
       </c>
       <c r="D50" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="E50" t="n">
-        <v>0.65625</v>
+        <v>1.25</v>
       </c>
       <c r="F50" t="n">
         <v>0.125</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4365</v>
+        <v>0.7124</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5965</v>
+        <v>1.19</v>
       </c>
       <c r="I50" t="n">
         <v>0.1292</v>
       </c>
       <c r="J50" t="n">
-        <v>0.1858</v>
+        <v>0.3318</v>
       </c>
       <c r="K50" t="n">
         <v>60</v>
@@ -7171,13 +7171,13 @@
         <v>37</v>
       </c>
       <c r="M50" t="n">
-        <v>1.3125</v>
+        <v>2.5</v>
       </c>
       <c r="N50" t="n">
         <v>0.08333</v>
       </c>
       <c r="O50" t="n">
-        <v>0.7514999999999999</v>
+        <v>1.1734</v>
       </c>
       <c r="P50" t="n">
         <v>0.04511</v>
@@ -7189,46 +7189,46 @@
         <v>0.08333</v>
       </c>
       <c r="S50" t="n">
-        <v>1.2735</v>
+        <v>0.9605</v>
       </c>
       <c r="T50" t="n">
-        <v>1.20489</v>
+        <v>0.89239</v>
       </c>
       <c r="U50" t="n">
-        <v>0.7594</v>
+        <v>0.5869</v>
       </c>
       <c r="V50" t="n">
-        <v>2.40978</v>
+        <v>1.78478</v>
       </c>
       <c r="W50" t="n">
-        <v>0.828</v>
+        <v>0.655</v>
       </c>
       <c r="X50" t="n">
         <v>0.08333</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.20489</v>
+        <v>0.89239</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.58</v>
+        <v>2.14</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.84</v>
+        <v>1.31</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.752</v>
+        <v>1.485</v>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>2406-32-16</t>
+          <t>2406-24-32</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 5/16-12 x 2 1/2-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 2 1/2-12 x 1 7/8-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>1 5/16-12</t>
+          <t>2 1/2-12</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>2 1/2-12 (female 37deg JIC)</t>
+          <t>1 7/8-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
@@ -7258,19 +7258,19 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.153 from the End A tip, inside the End A thread/groove zone (0.911); radial wall there min 0.025 at 0.911 from the tip (THIN)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.301 from the End A tip, inside the End A thread/groove zone (1.333); radial wall there min 0.412 at 1.333 from the tip (OK)</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>2406-32-16</t>
+          <t>2406-24-32</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2406-32-20</t>
+          <t>2406-32-16</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -7283,22 +7283,22 @@
         <v>2.88</v>
       </c>
       <c r="E51" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="F51" t="n">
         <v>0.125</v>
       </c>
       <c r="G51" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="H51" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="J51" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="K51" t="n">
         <v>60</v>
@@ -7307,13 +7307,13 @@
         <v>37</v>
       </c>
       <c r="M51" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="N51" t="n">
         <v>0.08333</v>
       </c>
       <c r="O51" t="n">
-        <v>0.7986</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="P51" t="n">
         <v>0.04511</v>
@@ -7352,19 +7352,19 @@
         <v>2.58</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AC51" t="n">
         <v>1.752</v>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>2406-32-20</t>
+          <t>2406-32-16</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>Female JIC x Male JIC Reducer/Expander, 1 5/8-12 x 2 1/2-12 (female 37deg JIC)</t>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 5/16-12 x 2 1/2-12 (female 37deg JIC)</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>1 5/8-12</t>
+          <t>1 5/16-12</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
@@ -7394,23 +7394,23 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.153 from the End A tip, inside the End A thread/groove zone (0.958); radial wall there min 0.146 at 0.958 from the tip (OK)</t>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.153 from the End A tip, inside the End A thread/groove zone (0.911); radial wall there min 0.025 at 0.911 from the tip (THIN)</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>2406-32-20</t>
+          <t>2406-32-16</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2406-32-24</t>
+          <t>2406-32-20</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="C52" t="n">
         <v>1.66277</v>
@@ -7419,22 +7419,22 @@
         <v>2.88</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="F52" t="n">
         <v>0.125</v>
       </c>
       <c r="G52" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1298</v>
+        <v>0.1288</v>
       </c>
       <c r="J52" t="n">
-        <v>0.2482</v>
+        <v>0.2382</v>
       </c>
       <c r="K52" t="n">
         <v>60</v>
@@ -7443,13 +7443,13 @@
         <v>37</v>
       </c>
       <c r="M52" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="N52" t="n">
         <v>0.08333</v>
       </c>
       <c r="O52" t="n">
-        <v>0.9234</v>
+        <v>0.7986</v>
       </c>
       <c r="P52" t="n">
         <v>0.04511</v>
@@ -7485,55 +7485,191 @@
         <v>1.25</v>
       </c>
       <c r="AA52" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.752</v>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>2406-32-20</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>Female JIC x Male JIC Reducer/Expander, 1 5/8-12 x 2 1/2-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>1 5/8-12</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (female 37deg JIC)</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.153 from the End A tip, inside the End A thread/groove zone (0.958); radial wall there min 0.146 at 0.958 from the tip (OK)</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>2406-32-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2406-32-24</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
         <v>2.61</v>
       </c>
-      <c r="AB52" t="n">
+      <c r="C53" t="n">
+        <v>1.66277</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="K53" t="n">
+        <v>60</v>
+      </c>
+      <c r="L53" t="n">
+        <v>37</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.9234</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1.2735</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0.7594</v>
+      </c>
+      <c r="V53" t="n">
+        <v>2.40978</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AB53" t="n">
         <v>1.31</v>
       </c>
-      <c r="AC52" t="n">
+      <c r="AC53" t="n">
         <v>1.782</v>
       </c>
-      <c r="AD52" t="inlineStr">
+      <c r="AD53" t="inlineStr">
         <is>
           <t>2406-32-24</t>
         </is>
       </c>
-      <c r="AE52" t="inlineStr">
+      <c r="AE53" t="inlineStr">
         <is>
           <t>Female JIC x Male JIC Reducer/Expander, 1 7/8-12 x 2 1/2-12 (female 37deg JIC)</t>
         </is>
       </c>
-      <c r="AF52" t="inlineStr">
+      <c r="AF53" t="inlineStr">
         <is>
           <t>2406</t>
         </is>
       </c>
-      <c r="AG52" t="inlineStr">
+      <c r="AG53" t="inlineStr">
         <is>
           <t>1 7/8-12</t>
         </is>
       </c>
-      <c r="AH52" t="inlineStr">
+      <c r="AH53" t="inlineStr">
         <is>
           <t>2 1/2-12 (female 37deg JIC)</t>
         </is>
       </c>
-      <c r="AI52" t="inlineStr">
+      <c r="AI53" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AJ52" t="inlineStr">
+      <c r="AJ53" t="inlineStr">
         <is>
           <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source) | MODEL: female 37deg JIC port (Brennan 2406 STEPs, one per female size -04..-32): thread minor = ASME B1.1 basic minor, 45deg countersink from the measured dia, minor bore to the measured depth, 37deg internal seat from the minor straight down to the bore (no flat) - measured at every size; the round collar at the female end on the STEP is NOT modelled (hex over the full body); male JIC end MS33656J (VERIFIED); bore D3 from the male tip to the seat</t>
         </is>
       </c>
-      <c r="AK52" t="inlineStr">
+      <c r="AK53" t="inlineStr">
         <is>
           <t>RESOLVED 2026-09-24 for female -08 ports (was: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.) -&gt; port measured on the Brennan 2406-08-08 STEP | female port reaches 0.183 from the End A tip, inside the End A thread/groove zone (1.083); radial wall there min 0.199 at 1.083 from the tip (OK)</t>
         </is>
       </c>
-      <c r="AL52" t="inlineStr">
+      <c r="AL53" t="inlineStr">
         <is>
           <t>2406-32-24</t>
         </is>
